--- a/metadata2.xlsx
+++ b/metadata2.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\stage_Curtin_Mahidol_2026\bobtail_pilot\bobtail_interactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2B76D9-BB0B-4073-9361-DF319C9B859F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0881A18A-D6ED-492D-8345-AC616873CDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A3C5114E-9B8E-4288-B332-3B9E578DDD5E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="metadata2" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3326" uniqueCount="721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3507" uniqueCount="721">
   <si>
     <t>picture</t>
   </si>
@@ -2673,7 +2673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F39935F-6883-4489-9BC2-6925FFCEA2E0}">
-  <dimension ref="A1:J1072"/>
+  <dimension ref="A1:J1108"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -21628,7 +21628,7 @@
         <v>265</v>
       </c>
       <c r="C593" s="2">
-        <v>7.2916666666666671E-2</v>
+        <v>0.57291666666666663</v>
       </c>
       <c r="D593" s="1" t="s">
         <v>38</v>
@@ -21660,7 +21660,7 @@
         <v>265</v>
       </c>
       <c r="C594" s="2">
-        <v>7.2916666666666671E-2</v>
+        <v>0.57291666666666663</v>
       </c>
       <c r="D594" s="1">
         <v>3</v>
@@ -31294,7 +31294,9 @@
       <c r="C895" s="11">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D895" s="10"/>
+      <c r="D895" s="10">
+        <v>4</v>
+      </c>
       <c r="E895" s="10" t="s">
         <v>536</v>
       </c>
@@ -31324,7 +31326,9 @@
       <c r="C896" s="11">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D896" s="10"/>
+      <c r="D896" s="10">
+        <v>6</v>
+      </c>
       <c r="E896" s="10" t="s">
         <v>536</v>
       </c>
@@ -31354,7 +31358,9 @@
       <c r="C897" s="11">
         <v>0.4375</v>
       </c>
-      <c r="D897" s="10"/>
+      <c r="D897" s="10">
+        <v>6</v>
+      </c>
       <c r="E897" s="10" t="s">
         <v>536</v>
       </c>
@@ -31384,7 +31390,9 @@
       <c r="C898" s="11">
         <v>0.44791666666666702</v>
       </c>
-      <c r="D898" s="10"/>
+      <c r="D898" s="10">
+        <v>6</v>
+      </c>
       <c r="E898" s="10" t="s">
         <v>536</v>
       </c>
@@ -31414,7 +31422,9 @@
       <c r="C899" s="11">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D899" s="10"/>
+      <c r="D899" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="E899" s="10" t="s">
         <v>536</v>
       </c>
@@ -31444,7 +31454,9 @@
       <c r="C900" s="11">
         <v>0.46875</v>
       </c>
-      <c r="D900" s="10"/>
+      <c r="D900" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="E900" s="10" t="s">
         <v>536</v>
       </c>
@@ -31474,7 +31486,9 @@
       <c r="C901" s="11">
         <v>0.47916666666666702</v>
       </c>
-      <c r="D901" s="10"/>
+      <c r="D901" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="E901" s="10" t="s">
         <v>536</v>
       </c>
@@ -31504,7 +31518,9 @@
       <c r="C902" s="11">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D902" s="10"/>
+      <c r="D902" s="10">
+        <v>6</v>
+      </c>
       <c r="E902" s="10" t="s">
         <v>536</v>
       </c>
@@ -31534,7 +31550,9 @@
       <c r="C903" s="11">
         <v>0.40625</v>
       </c>
-      <c r="D903" s="10"/>
+      <c r="D903" s="10">
+        <v>6</v>
+      </c>
       <c r="E903" s="10" t="s">
         <v>536</v>
       </c>
@@ -31564,7 +31582,9 @@
       <c r="C904" s="11">
         <v>0.41666666666666702</v>
       </c>
-      <c r="D904" s="10"/>
+      <c r="D904" s="10">
+        <v>6</v>
+      </c>
       <c r="E904" s="10" t="s">
         <v>536</v>
       </c>
@@ -31594,7 +31614,9 @@
       <c r="C905" s="11">
         <v>0.42708333333333298</v>
       </c>
-      <c r="D905" s="10"/>
+      <c r="D905" s="10">
+        <v>6</v>
+      </c>
       <c r="E905" s="10" t="s">
         <v>536</v>
       </c>
@@ -31624,7 +31646,9 @@
       <c r="C906" s="11">
         <v>0.4375</v>
       </c>
-      <c r="D906" s="10"/>
+      <c r="D906" s="10">
+        <v>6</v>
+      </c>
       <c r="E906" s="10" t="s">
         <v>536</v>
       </c>
@@ -31654,7 +31678,9 @@
       <c r="C907" s="11">
         <v>0.44791666666666702</v>
       </c>
-      <c r="D907" s="10"/>
+      <c r="D907" s="10">
+        <v>4</v>
+      </c>
       <c r="E907" s="10" t="s">
         <v>536</v>
       </c>
@@ -31676,20 +31702,22 @@
     </row>
     <row r="908" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A908" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B908" s="10" t="s">
         <v>79</v>
       </c>
       <c r="C908" s="11">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D908" s="10"/>
+        <v>0.44791666666666702</v>
+      </c>
+      <c r="D908" s="10">
+        <v>6</v>
+      </c>
       <c r="E908" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F908" s="10">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G908" s="10">
         <v>16.7</v>
@@ -31706,20 +31734,22 @@
     </row>
     <row r="909" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A909" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B909" s="10" t="s">
         <v>79</v>
       </c>
       <c r="C909" s="11">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D909" s="10"/>
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D909" s="10">
+        <v>6</v>
+      </c>
       <c r="E909" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F909" s="10">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G909" s="10">
         <v>16.7</v>
@@ -31736,15 +31766,17 @@
     </row>
     <row r="910" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A910" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B910" s="10" t="s">
         <v>79</v>
       </c>
       <c r="C910" s="11">
-        <v>0.61458333333333337</v>
-      </c>
-      <c r="D910" s="10"/>
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D910" s="10">
+        <v>3</v>
+      </c>
       <c r="E910" s="10" t="s">
         <v>536</v>
       </c>
@@ -31766,50 +31798,54 @@
     </row>
     <row r="911" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A911" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B911" s="10" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="C911" s="11">
-        <v>0.38541666666666669</v>
-      </c>
-      <c r="D911" s="10"/>
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D911" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="E911" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F911" s="10">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G911" s="10">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="H911" s="10">
-        <v>23.9</v>
+        <v>20.3</v>
       </c>
       <c r="I911" s="10">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J911" s="10">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="912" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A912" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B912" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C912" s="11">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="D912" s="10"/>
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="D912" s="10">
+        <v>6</v>
+      </c>
       <c r="E912" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F912" s="10">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G912" s="10">
         <v>16.5</v>
@@ -31826,20 +31862,22 @@
     </row>
     <row r="913" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A913" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B913" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C913" s="11">
-        <v>0.40625</v>
-      </c>
-      <c r="D913" s="10"/>
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D913" s="10">
+        <v>6</v>
+      </c>
       <c r="E913" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F913" s="10">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G913" s="10">
         <v>16.5</v>
@@ -31856,20 +31894,22 @@
     </row>
     <row r="914" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A914" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B914" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C914" s="11">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="D914" s="10"/>
+        <v>0.40625</v>
+      </c>
+      <c r="D914" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="E914" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F914" s="10">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G914" s="10">
         <v>16.5</v>
@@ -31886,20 +31926,22 @@
     </row>
     <row r="915" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A915" s="10" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B915" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C915" s="11">
-        <v>0.42708333333333298</v>
-      </c>
-      <c r="D915" s="10"/>
+        <v>0.40625</v>
+      </c>
+      <c r="D915" s="10">
+        <v>5</v>
+      </c>
       <c r="E915" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F915" s="10">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G915" s="10">
         <v>16.5</v>
@@ -31916,20 +31958,22 @@
     </row>
     <row r="916" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A916" s="10" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B916" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C916" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="D916" s="10"/>
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="D916" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="E916" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F916" s="10">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G916" s="10">
         <v>16.5</v>
@@ -31946,20 +31990,22 @@
     </row>
     <row r="917" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A917" s="10" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B917" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C917" s="11">
-        <v>0.44791666666666602</v>
-      </c>
-      <c r="D917" s="10"/>
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="D917" s="10">
+        <v>5</v>
+      </c>
       <c r="E917" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F917" s="10">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G917" s="10">
         <v>16.5</v>
@@ -31976,20 +32022,22 @@
     </row>
     <row r="918" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A918" s="10" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B918" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C918" s="11">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D918" s="10"/>
+        <v>0.42708333333333298</v>
+      </c>
+      <c r="D918" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="E918" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F918" s="10">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G918" s="10">
         <v>16.5</v>
@@ -32006,20 +32054,22 @@
     </row>
     <row r="919" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A919" s="10" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B919" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C919" s="11">
-        <v>0.46875</v>
-      </c>
-      <c r="D919" s="10"/>
+        <v>0.42708333333333298</v>
+      </c>
+      <c r="D919" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="E919" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F919" s="10">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G919" s="10">
         <v>16.5</v>
@@ -32036,20 +32086,22 @@
     </row>
     <row r="920" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A920" s="10" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="B920" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C920" s="11">
-        <v>0.47916666666666602</v>
-      </c>
-      <c r="D920" s="10"/>
+        <v>0.42708333333333298</v>
+      </c>
+      <c r="D920" s="10">
+        <v>4</v>
+      </c>
       <c r="E920" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F920" s="10">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G920" s="10">
         <v>16.5</v>
@@ -32066,20 +32118,22 @@
     </row>
     <row r="921" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A921" s="10" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="B921" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C921" s="11">
-        <v>0.48958333333333298</v>
-      </c>
-      <c r="D921" s="10"/>
+        <v>0.4375</v>
+      </c>
+      <c r="D921" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="E921" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F921" s="10">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G921" s="10">
         <v>16.5</v>
@@ -32096,20 +32150,22 @@
     </row>
     <row r="922" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A922" s="10" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="B922" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C922" s="11">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D922" s="10"/>
+        <v>0.4375</v>
+      </c>
+      <c r="D922" s="10">
+        <v>4</v>
+      </c>
       <c r="E922" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F922" s="10">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G922" s="10">
         <v>16.5</v>
@@ -32126,315 +32182,337 @@
     </row>
     <row r="923" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A923" s="10" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="B923" s="10" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="C923" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="D923" s="10"/>
+        <v>0.44791666666666602</v>
+      </c>
+      <c r="D923" s="10">
+        <v>4</v>
+      </c>
       <c r="E923" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F923" s="10">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G923" s="10">
         <v>16.5</v>
       </c>
       <c r="H923" s="10">
-        <v>15</v>
+        <v>23.9</v>
       </c>
       <c r="I923" s="10">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="J923" s="10">
-        <v>100</v>
+        <v>36</v>
       </c>
     </row>
     <row r="924" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A924" s="10" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="B924" s="10" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="C924" s="11">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="D924" s="10"/>
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D924" s="10">
+        <v>1</v>
+      </c>
       <c r="E924" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F924" s="10">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G924" s="10">
         <v>16.5</v>
       </c>
       <c r="H924" s="10">
-        <v>15</v>
+        <v>23.9</v>
       </c>
       <c r="I924" s="10">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="J924" s="10">
-        <v>100</v>
+        <v>36</v>
       </c>
     </row>
     <row r="925" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A925" s="10" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="B925" s="10" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="C925" s="11">
-        <v>0.52083333333333304</v>
-      </c>
-      <c r="D925" s="10"/>
+        <v>0.46875</v>
+      </c>
+      <c r="D925" s="10">
+        <v>1</v>
+      </c>
       <c r="E925" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F925" s="10">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G925" s="10">
         <v>16.5</v>
       </c>
       <c r="H925" s="10">
-        <v>15</v>
+        <v>23.9</v>
       </c>
       <c r="I925" s="10">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="J925" s="10">
-        <v>100</v>
+        <v>36</v>
       </c>
     </row>
     <row r="926" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A926" s="10" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="B926" s="10" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="C926" s="11">
-        <v>0.53125</v>
-      </c>
-      <c r="D926" s="10"/>
+        <v>0.46875</v>
+      </c>
+      <c r="D926" s="10">
+        <v>4</v>
+      </c>
       <c r="E926" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F926" s="10">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G926" s="10">
         <v>16.5</v>
       </c>
       <c r="H926" s="10">
-        <v>15</v>
+        <v>23.9</v>
       </c>
       <c r="I926" s="10">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="J926" s="10">
-        <v>100</v>
+        <v>36</v>
       </c>
     </row>
     <row r="927" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A927" s="10" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="B927" s="10" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="C927" s="11">
-        <v>0.54166666666666696</v>
-      </c>
-      <c r="D927" s="10"/>
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="D927" s="10">
+        <v>8</v>
+      </c>
       <c r="E927" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F927" s="10">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="G927" s="10">
         <v>16.5</v>
       </c>
       <c r="H927" s="10">
-        <v>15</v>
+        <v>23.9</v>
       </c>
       <c r="I927" s="10">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="J927" s="10">
-        <v>100</v>
+        <v>36</v>
       </c>
     </row>
     <row r="928" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A928" s="10" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="B928" s="10" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="C928" s="11">
-        <v>0.55208333333333304</v>
-      </c>
-      <c r="D928" s="10"/>
+        <v>0.48958333333333298</v>
+      </c>
+      <c r="D928" s="10">
+        <v>1</v>
+      </c>
       <c r="E928" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F928" s="10">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="G928" s="10">
         <v>16.5</v>
       </c>
       <c r="H928" s="10">
-        <v>15</v>
+        <v>23.9</v>
       </c>
       <c r="I928" s="10">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="J928" s="10">
-        <v>100</v>
+        <v>36</v>
       </c>
     </row>
     <row r="929" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A929" s="10" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="B929" s="10" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="C929" s="11">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D929" s="10"/>
+        <v>0.48958333333333298</v>
+      </c>
+      <c r="D929" s="10">
+        <v>8</v>
+      </c>
       <c r="E929" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F929" s="10">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="G929" s="10">
-        <v>15.6</v>
+        <v>16.5</v>
       </c>
       <c r="H929" s="10">
-        <v>18.2</v>
+        <v>23.9</v>
       </c>
       <c r="I929" s="10">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="J929" s="10">
-        <v>83</v>
+        <v>36</v>
       </c>
     </row>
     <row r="930" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A930" s="10" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="B930" s="10" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="C930" s="11">
-        <v>0.36458333333333331</v>
-      </c>
-      <c r="D930" s="10"/>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D930" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="E930" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F930" s="10">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="G930" s="10">
-        <v>15.6</v>
+        <v>16.5</v>
       </c>
       <c r="H930" s="10">
-        <v>18.2</v>
+        <v>23.9</v>
       </c>
       <c r="I930" s="10">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="J930" s="10">
-        <v>83</v>
+        <v>36</v>
       </c>
     </row>
     <row r="931" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A931" s="10" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="B931" s="10" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C931" s="11">
-        <v>0.375</v>
-      </c>
-      <c r="D931" s="10"/>
+        <v>0.5</v>
+      </c>
+      <c r="D931" s="10">
+        <v>4</v>
+      </c>
       <c r="E931" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F931" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G931" s="10">
-        <v>15.6</v>
+        <v>16.5</v>
       </c>
       <c r="H931" s="10">
-        <v>18.2</v>
+        <v>15</v>
       </c>
       <c r="I931" s="10">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J931" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="932" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A932" s="10" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="B932" s="10" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C932" s="11">
-        <v>0.38541666666666702</v>
-      </c>
-      <c r="D932" s="10"/>
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D932" s="10">
+        <v>4</v>
+      </c>
       <c r="E932" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F932" s="10">
+        <v>16</v>
+      </c>
+      <c r="G932" s="10">
+        <v>16.5</v>
+      </c>
+      <c r="H932" s="10">
         <v>15</v>
       </c>
-      <c r="G932" s="10">
-        <v>15.6</v>
-      </c>
-      <c r="H932" s="10">
-        <v>18.2</v>
-      </c>
       <c r="I932" s="10">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J932" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="933" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A933" s="10" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="B933" s="10" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C933" s="11">
-        <v>0.39583333333333298</v>
-      </c>
-      <c r="D933" s="10"/>
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="D933" s="10">
+        <v>4</v>
+      </c>
       <c r="E933" s="10" t="s">
         <v>536</v>
       </c>
@@ -32442,29 +32520,31 @@
         <v>16</v>
       </c>
       <c r="G933" s="10">
-        <v>15.6</v>
+        <v>16.5</v>
       </c>
       <c r="H933" s="10">
-        <v>18.2</v>
+        <v>15</v>
       </c>
       <c r="I933" s="10">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J933" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="934" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A934" s="10" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="B934" s="10" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C934" s="11">
-        <v>0.40625</v>
-      </c>
-      <c r="D934" s="10"/>
+        <v>0.53125</v>
+      </c>
+      <c r="D934" s="10">
+        <v>4</v>
+      </c>
       <c r="E934" s="10" t="s">
         <v>536</v>
       </c>
@@ -32472,59 +32552,63 @@
         <v>16</v>
       </c>
       <c r="G934" s="10">
-        <v>15.6</v>
+        <v>16.5</v>
       </c>
       <c r="H934" s="10">
-        <v>18.2</v>
+        <v>15</v>
       </c>
       <c r="I934" s="10">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J934" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="935" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A935" s="10" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="B935" s="10" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C935" s="11">
-        <v>0.41666666666666602</v>
-      </c>
-      <c r="D935" s="10"/>
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="D935" s="10">
+        <v>4</v>
+      </c>
       <c r="E935" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F935" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G935" s="10">
-        <v>15.6</v>
+        <v>16.5</v>
       </c>
       <c r="H935" s="10">
-        <v>18.2</v>
+        <v>15</v>
       </c>
       <c r="I935" s="10">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J935" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="936" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A936" s="10" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="B936" s="10" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C936" s="11">
-        <v>0.42708333333333298</v>
-      </c>
-      <c r="D936" s="10"/>
+        <v>0.55208333333333304</v>
+      </c>
+      <c r="D936" s="10">
+        <v>4</v>
+      </c>
       <c r="E936" s="10" t="s">
         <v>536</v>
       </c>
@@ -32532,479 +32616,511 @@
         <v>17</v>
       </c>
       <c r="G936" s="10">
-        <v>15.6</v>
+        <v>16.5</v>
       </c>
       <c r="H936" s="10">
-        <v>18.2</v>
+        <v>15</v>
       </c>
       <c r="I936" s="10">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J936" s="10">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="937" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A937" s="10" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B937" s="10" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="C937" s="11">
-        <v>0.40625</v>
-      </c>
-      <c r="D937" s="10"/>
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D937" s="10">
+        <v>6</v>
+      </c>
       <c r="E937" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F937" s="10">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G937" s="10">
-        <v>18</v>
+        <v>15.6</v>
       </c>
       <c r="H937" s="10">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="I937" s="10">
         <v>95</v>
       </c>
       <c r="J937" s="10">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="938" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A938" s="10" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="B938" s="10" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="C938" s="11">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="D938" s="10"/>
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="D938" s="10">
+        <v>6</v>
+      </c>
       <c r="E938" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F938" s="10">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G938" s="10">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="H938" s="10">
-        <v>18.100000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="I938" s="10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J938" s="10">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="939" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A939" s="10" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B939" s="10" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="C939" s="11">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D939" s="10"/>
+        <v>0.375</v>
+      </c>
+      <c r="D939" s="10">
+        <v>6</v>
+      </c>
       <c r="E939" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F939" s="10">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G939" s="10">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="H939" s="10">
-        <v>18.100000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="I939" s="10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J939" s="10">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="940" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A940" s="10" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="B940" s="10" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="C940" s="11">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="D940" s="10"/>
+        <v>0.38541666666666702</v>
+      </c>
+      <c r="D940" s="10">
+        <v>6</v>
+      </c>
       <c r="E940" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F940" s="10">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G940" s="10">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="H940" s="10">
-        <v>18.100000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="I940" s="10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J940" s="10">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="941" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A941" s="10" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="B941" s="10" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="C941" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="D941" s="10"/>
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="D941" s="10">
+        <v>6</v>
+      </c>
       <c r="E941" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F941" s="10">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="G941" s="10">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="H941" s="10">
-        <v>18.100000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="I941" s="10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J941" s="10">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="942" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A942" s="10" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="B942" s="10" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="C942" s="11">
-        <v>0.44791666666666702</v>
-      </c>
-      <c r="D942" s="10"/>
+        <v>0.40625</v>
+      </c>
+      <c r="D942" s="10">
+        <v>6</v>
+      </c>
       <c r="E942" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F942" s="10">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G942" s="10">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="H942" s="10">
-        <v>18.100000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="I942" s="10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J942" s="10">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="943" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A943" s="10" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="B943" s="10" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="C943" s="11">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D943" s="10"/>
+        <v>0.41666666666666602</v>
+      </c>
+      <c r="D943" s="10">
+        <v>6</v>
+      </c>
       <c r="E943" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F943" s="10">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G943" s="10">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="H943" s="10">
-        <v>18.100000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="I943" s="10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J943" s="10">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="944" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A944" s="10" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="B944" s="10" t="s">
-        <v>216</v>
+        <v>139</v>
       </c>
       <c r="C944" s="11">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="D944" s="10"/>
+        <v>0.42708333333333298</v>
+      </c>
+      <c r="D944" s="10">
+        <v>6</v>
+      </c>
       <c r="E944" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F944" s="10">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G944" s="10">
-        <v>11.8</v>
+        <v>15.6</v>
       </c>
       <c r="H944" s="10">
-        <v>15</v>
+        <v>18.2</v>
       </c>
       <c r="I944" s="10">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J944" s="10">
-        <v>46</v>
+        <v>83</v>
       </c>
     </row>
     <row r="945" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A945" s="10" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="B945" s="10" t="s">
-        <v>216</v>
+        <v>161</v>
       </c>
       <c r="C945" s="11">
-        <v>0.48958333333333331</v>
-      </c>
-      <c r="D945" s="10"/>
+        <v>0.40625</v>
+      </c>
+      <c r="D945" s="10">
+        <v>6</v>
+      </c>
       <c r="E945" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F945" s="10">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="G945" s="10">
-        <v>11.8</v>
+        <v>18</v>
       </c>
       <c r="H945" s="10">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I945" s="10">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J945" s="10">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="946" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A946" s="10" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="B946" s="10" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="C946" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="D946" s="10"/>
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D946" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="E946" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F946" s="10">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G946" s="10">
-        <v>11.6</v>
+        <v>15.1</v>
       </c>
       <c r="H946" s="10">
-        <v>16.3</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="I946" s="10">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J946" s="10">
-        <v>48</v>
+        <v>76</v>
       </c>
     </row>
     <row r="947" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A947" s="10" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="B947" s="10" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="C947" s="11">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D947" s="10"/>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D947" s="10">
+        <v>4</v>
+      </c>
       <c r="E947" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F947" s="10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G947" s="10">
-        <v>11.6</v>
+        <v>15.1</v>
       </c>
       <c r="H947" s="10">
-        <v>16.3</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="I947" s="10">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J947" s="10">
-        <v>48</v>
+        <v>76</v>
       </c>
     </row>
     <row r="948" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A948" s="10" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="B948" s="10" t="s">
-        <v>265</v>
+        <v>190</v>
       </c>
       <c r="C948" s="11">
-        <v>0.46875</v>
-      </c>
-      <c r="D948" s="10"/>
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D948" s="10">
+        <v>4</v>
+      </c>
       <c r="E948" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F948" s="10">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G948" s="10">
-        <v>12</v>
+        <v>15.1</v>
       </c>
       <c r="H948" s="10">
-        <v>18.399999999999999</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="I948" s="10">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J948" s="10">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="949" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A949" s="10" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="B949" s="10" t="s">
-        <v>265</v>
+        <v>190</v>
       </c>
       <c r="C949" s="11">
-        <v>0.5625</v>
-      </c>
-      <c r="D949" s="10"/>
+        <v>0.4375</v>
+      </c>
+      <c r="D949" s="10">
+        <v>4</v>
+      </c>
       <c r="E949" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F949" s="10">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G949" s="10">
-        <v>12</v>
+        <v>15.1</v>
       </c>
       <c r="H949" s="10">
-        <v>18.399999999999999</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="I949" s="10">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J949" s="10">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="950" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A950" s="10" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="B950" s="10" t="s">
-        <v>294</v>
+        <v>190</v>
       </c>
       <c r="C950" s="11">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D950" s="10"/>
+        <v>0.44791666666666702</v>
+      </c>
+      <c r="D950" s="10">
+        <v>6</v>
+      </c>
       <c r="E950" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F950" s="10">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G950" s="10">
-        <v>13.3</v>
+        <v>15.1</v>
       </c>
       <c r="H950" s="10">
-        <v>21.1</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="I950" s="10">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="J950" s="10">
-        <v>47</v>
+        <v>76</v>
       </c>
     </row>
     <row r="951" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A951" s="10" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="B951" s="10" t="s">
-        <v>294</v>
+        <v>190</v>
       </c>
       <c r="C951" s="11">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="D951" s="10"/>
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D951" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="E951" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F951" s="10">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G951" s="10">
-        <v>13.3</v>
+        <v>15.1</v>
       </c>
       <c r="H951" s="10">
-        <v>21.1</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="I951" s="10">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="J951" s="10">
-        <v>47</v>
+        <v>76</v>
       </c>
     </row>
     <row r="952" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A952" s="10" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="B952" s="10" t="s">
-        <v>294</v>
+        <v>190</v>
       </c>
       <c r="C952" s="11">
-        <v>0.46875</v>
-      </c>
-      <c r="D952" s="10"/>
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D952" s="10">
+        <v>1</v>
+      </c>
       <c r="E952" s="10" t="s">
         <v>536</v>
       </c>
@@ -33012,329 +33128,351 @@
         <v>38</v>
       </c>
       <c r="G952" s="10">
-        <v>13.3</v>
+        <v>15.1</v>
       </c>
       <c r="H952" s="10">
-        <v>21.1</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="I952" s="10">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="J952" s="10">
-        <v>47</v>
+        <v>76</v>
       </c>
     </row>
     <row r="953" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A953" s="10" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B953" s="10" t="s">
-        <v>294</v>
+        <v>216</v>
       </c>
       <c r="C953" s="11">
         <v>0.47916666666666669</v>
       </c>
-      <c r="D953" s="10"/>
+      <c r="D953" s="10">
+        <v>1</v>
+      </c>
       <c r="E953" s="10" t="s">
         <v>536</v>
       </c>
       <c r="F953" s="10">
+        <v>33</v>
+      </c>
+      <c r="G953" s="10">
+        <v>11.8</v>
+      </c>
+      <c r="H953" s="10">
+        <v>15</v>
+      </c>
+      <c r="I953" s="10">
+        <v>65</v>
+      </c>
+      <c r="J953" s="10">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="954" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A954" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="B954" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="C954" s="11">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="D954" s="10">
+        <v>1</v>
+      </c>
+      <c r="E954" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="F954" s="10">
+        <v>34</v>
+      </c>
+      <c r="G954" s="10">
+        <v>11.8</v>
+      </c>
+      <c r="H954" s="10">
+        <v>15</v>
+      </c>
+      <c r="I954" s="10">
+        <v>65</v>
+      </c>
+      <c r="J954" s="10">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="955" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A955" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="B955" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C955" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="D955" s="10">
+        <v>7</v>
+      </c>
+      <c r="E955" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="F955" s="10">
+        <v>31</v>
+      </c>
+      <c r="G955" s="10">
+        <v>11.6</v>
+      </c>
+      <c r="H955" s="10">
+        <v>16.3</v>
+      </c>
+      <c r="I955" s="10">
+        <v>70</v>
+      </c>
+      <c r="J955" s="10">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="956" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A956" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="B956" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C956" s="11">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D956" s="10">
+        <v>8</v>
+      </c>
+      <c r="E956" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="F956" s="10">
+        <v>28</v>
+      </c>
+      <c r="G956" s="10">
+        <v>11.6</v>
+      </c>
+      <c r="H956" s="10">
+        <v>16.3</v>
+      </c>
+      <c r="I956" s="10">
+        <v>70</v>
+      </c>
+      <c r="J956" s="10">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="957" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A957" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="B957" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="C957" s="11">
+        <v>0.46875</v>
+      </c>
+      <c r="D957" s="10">
+        <v>6</v>
+      </c>
+      <c r="E957" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="F957" s="10">
+        <v>17</v>
+      </c>
+      <c r="G957" s="10">
+        <v>12</v>
+      </c>
+      <c r="H957" s="10">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="I957" s="10">
+        <v>80</v>
+      </c>
+      <c r="J957" s="10">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="958" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A958" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="B958" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="C958" s="11">
+        <v>0.5625</v>
+      </c>
+      <c r="D958" s="10">
+        <v>6</v>
+      </c>
+      <c r="E958" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="F958" s="10">
+        <v>36</v>
+      </c>
+      <c r="G958" s="10">
+        <v>12</v>
+      </c>
+      <c r="H958" s="10">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="I958" s="10">
+        <v>80</v>
+      </c>
+      <c r="J958" s="10">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="959" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A959" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="B959" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="C959" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D959" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G953" s="10">
+      <c r="E959" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="F959" s="10">
+        <v>26</v>
+      </c>
+      <c r="G959" s="10">
         <v>13.3</v>
       </c>
-      <c r="H953" s="10">
+      <c r="H959" s="10">
         <v>21.1</v>
       </c>
-      <c r="I953" s="10">
+      <c r="I959" s="10">
         <v>81</v>
       </c>
-      <c r="J953" s="10">
+      <c r="J959" s="10">
         <v>47</v>
       </c>
     </row>
-    <row r="954" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A954" s="12" t="s">
-        <v>597</v>
-      </c>
-      <c r="B954" s="12" t="s">
-        <v>713</v>
-      </c>
-      <c r="C954" s="13">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D954" s="12"/>
-      <c r="E954" s="12" t="s">
-        <v>596</v>
-      </c>
-      <c r="F954" s="12">
-        <v>21</v>
-      </c>
-      <c r="G954" s="12">
-        <v>14.1</v>
-      </c>
-      <c r="H954" s="12">
-        <v>19.7</v>
-      </c>
-      <c r="I954" s="12">
-        <v>100</v>
-      </c>
-      <c r="J954" s="12">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="955" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A955" s="12" t="s">
-        <v>598</v>
-      </c>
-      <c r="B955" s="12" t="s">
-        <v>713</v>
-      </c>
-      <c r="C955" s="13">
-        <v>0.53125</v>
-      </c>
-      <c r="D955" s="12"/>
-      <c r="E955" s="12" t="s">
-        <v>596</v>
-      </c>
-      <c r="F955" s="12">
-        <v>21</v>
-      </c>
-      <c r="G955" s="12">
-        <v>14.1</v>
-      </c>
-      <c r="H955" s="12">
-        <v>19.7</v>
-      </c>
-      <c r="I955" s="12">
-        <v>100</v>
-      </c>
-      <c r="J955" s="12">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="956" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A956" s="12" t="s">
-        <v>599</v>
-      </c>
-      <c r="B956" s="12" t="s">
-        <v>713</v>
-      </c>
-      <c r="C956" s="13">
-        <v>0.54166666666666696</v>
-      </c>
-      <c r="D956" s="12"/>
-      <c r="E956" s="12" t="s">
-        <v>596</v>
-      </c>
-      <c r="F956" s="12">
-        <v>21</v>
-      </c>
-      <c r="G956" s="12">
-        <v>14.1</v>
-      </c>
-      <c r="H956" s="12">
-        <v>19.7</v>
-      </c>
-      <c r="I956" s="12">
-        <v>100</v>
-      </c>
-      <c r="J956" s="12">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="957" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A957" s="12" t="s">
-        <v>600</v>
-      </c>
-      <c r="B957" s="12" t="s">
-        <v>713</v>
-      </c>
-      <c r="C957" s="13">
-        <v>0.55208333333333304</v>
-      </c>
-      <c r="D957" s="12"/>
-      <c r="E957" s="12" t="s">
-        <v>596</v>
-      </c>
-      <c r="F957" s="12">
-        <v>21</v>
-      </c>
-      <c r="G957" s="12">
-        <v>14.1</v>
-      </c>
-      <c r="H957" s="12">
-        <v>19.7</v>
-      </c>
-      <c r="I957" s="12">
-        <v>100</v>
-      </c>
-      <c r="J957" s="12">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="958" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A958" s="12" t="s">
-        <v>601</v>
-      </c>
-      <c r="B958" s="12" t="s">
-        <v>713</v>
-      </c>
-      <c r="C958" s="13">
-        <v>0.5625</v>
-      </c>
-      <c r="D958" s="12"/>
-      <c r="E958" s="12" t="s">
-        <v>596</v>
-      </c>
-      <c r="F958" s="12">
-        <v>23</v>
-      </c>
-      <c r="G958" s="12">
-        <v>14.1</v>
-      </c>
-      <c r="H958" s="12">
-        <v>19.7</v>
-      </c>
-      <c r="I958" s="12">
-        <v>100</v>
-      </c>
-      <c r="J958" s="12">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="959" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A959" s="12" t="s">
-        <v>602</v>
-      </c>
-      <c r="B959" s="12" t="s">
-        <v>713</v>
-      </c>
-      <c r="C959" s="13">
-        <v>0.57291666666666696</v>
-      </c>
-      <c r="D959" s="12"/>
-      <c r="E959" s="12" t="s">
-        <v>596</v>
-      </c>
-      <c r="F959" s="12">
-        <v>24</v>
-      </c>
-      <c r="G959" s="12">
-        <v>14.1</v>
-      </c>
-      <c r="H959" s="12">
-        <v>19.7</v>
-      </c>
-      <c r="I959" s="12">
-        <v>100</v>
-      </c>
-      <c r="J959" s="12">
-        <v>54</v>
-      </c>
-    </row>
     <row r="960" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A960" s="12" t="s">
-        <v>603</v>
-      </c>
-      <c r="B960" s="12" t="s">
-        <v>713</v>
-      </c>
-      <c r="C960" s="13">
-        <v>0.58333333333333304</v>
-      </c>
-      <c r="D960" s="12"/>
-      <c r="E960" s="12" t="s">
-        <v>596</v>
-      </c>
-      <c r="F960" s="12">
-        <v>26</v>
-      </c>
-      <c r="G960" s="12">
-        <v>14.1</v>
-      </c>
-      <c r="H960" s="12">
-        <v>19.7</v>
-      </c>
-      <c r="I960" s="12">
-        <v>100</v>
-      </c>
-      <c r="J960" s="12">
-        <v>54</v>
+      <c r="A960" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="B960" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="C960" s="11">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D960" s="10">
+        <v>5</v>
+      </c>
+      <c r="E960" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="F960" s="10">
+        <v>30</v>
+      </c>
+      <c r="G960" s="10">
+        <v>13.3</v>
+      </c>
+      <c r="H960" s="10">
+        <v>21.1</v>
+      </c>
+      <c r="I960" s="10">
+        <v>81</v>
+      </c>
+      <c r="J960" s="10">
+        <v>47</v>
       </c>
     </row>
     <row r="961" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A961" s="12" t="s">
-        <v>604</v>
-      </c>
-      <c r="B961" s="12" t="s">
-        <v>713</v>
-      </c>
-      <c r="C961" s="13">
-        <v>0.59375</v>
-      </c>
-      <c r="D961" s="12"/>
-      <c r="E961" s="12" t="s">
-        <v>596</v>
-      </c>
-      <c r="F961" s="12">
-        <v>26</v>
-      </c>
-      <c r="G961" s="12">
-        <v>14.1</v>
-      </c>
-      <c r="H961" s="12">
-        <v>19.7</v>
-      </c>
-      <c r="I961" s="12">
-        <v>100</v>
-      </c>
-      <c r="J961" s="12">
-        <v>54</v>
+      <c r="A961" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="B961" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="C961" s="11">
+        <v>0.46875</v>
+      </c>
+      <c r="D961" s="10">
+        <v>1</v>
+      </c>
+      <c r="E961" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="F961" s="10">
+        <v>38</v>
+      </c>
+      <c r="G961" s="10">
+        <v>13.3</v>
+      </c>
+      <c r="H961" s="10">
+        <v>21.1</v>
+      </c>
+      <c r="I961" s="10">
+        <v>81</v>
+      </c>
+      <c r="J961" s="10">
+        <v>47</v>
       </c>
     </row>
     <row r="962" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A962" s="12" t="s">
-        <v>605</v>
-      </c>
-      <c r="B962" s="12" t="s">
-        <v>713</v>
-      </c>
-      <c r="C962" s="13">
-        <v>0.60416666666666596</v>
-      </c>
-      <c r="D962" s="12"/>
-      <c r="E962" s="12" t="s">
-        <v>596</v>
-      </c>
-      <c r="F962" s="12">
-        <v>25</v>
-      </c>
-      <c r="G962" s="12">
-        <v>14.1</v>
-      </c>
-      <c r="H962" s="12">
-        <v>19.7</v>
-      </c>
-      <c r="I962" s="12">
-        <v>100</v>
-      </c>
-      <c r="J962" s="12">
-        <v>54</v>
+      <c r="A962" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="B962" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="C962" s="11">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D962" s="10">
+        <v>4</v>
+      </c>
+      <c r="E962" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="F962" s="10">
+        <v>38</v>
+      </c>
+      <c r="G962" s="10">
+        <v>13.3</v>
+      </c>
+      <c r="H962" s="10">
+        <v>21.1</v>
+      </c>
+      <c r="I962" s="10">
+        <v>81</v>
+      </c>
+      <c r="J962" s="10">
+        <v>47</v>
       </c>
     </row>
     <row r="963" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A963" s="12" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="B963" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C963" s="13">
-        <v>0.48958333333333331</v>
-      </c>
-      <c r="D963" s="12"/>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D963" s="12">
+        <v>1</v>
+      </c>
       <c r="E963" s="12" t="s">
         <v>596</v>
       </c>
@@ -33342,304 +33480,324 @@
         <v>21</v>
       </c>
       <c r="G963" s="12">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="H963" s="12">
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
       <c r="I963" s="12">
         <v>100</v>
       </c>
       <c r="J963" s="12">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="964" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A964" s="12" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="B964" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C964" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="D964" s="12"/>
+        <v>0.53125</v>
+      </c>
+      <c r="D964" s="12">
+        <v>6</v>
+      </c>
       <c r="E964" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F964" s="12">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G964" s="12">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="H964" s="12">
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
       <c r="I964" s="12">
         <v>100</v>
       </c>
       <c r="J964" s="12">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="965" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A965" s="12" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="B965" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C965" s="13">
-        <v>0.51041666666666696</v>
-      </c>
-      <c r="D965" s="12"/>
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="D965" s="12">
+        <v>6</v>
+      </c>
       <c r="E965" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F965" s="12">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G965" s="12">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="H965" s="12">
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
       <c r="I965" s="12">
         <v>100</v>
       </c>
       <c r="J965" s="12">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="966" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A966" s="12" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="B966" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C966" s="13">
-        <v>0.52083333333333304</v>
-      </c>
-      <c r="D966" s="12"/>
+        <v>0.55208333333333304</v>
+      </c>
+      <c r="D966" s="12">
+        <v>6</v>
+      </c>
       <c r="E966" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F966" s="12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G966" s="12">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="H966" s="12">
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
       <c r="I966" s="12">
         <v>100</v>
       </c>
       <c r="J966" s="12">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="967" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A967" s="12" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="B967" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C967" s="13">
-        <v>0.53125</v>
-      </c>
-      <c r="D967" s="12"/>
+        <v>0.5625</v>
+      </c>
+      <c r="D967" s="12">
+        <v>6</v>
+      </c>
       <c r="E967" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F967" s="12">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G967" s="12">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="H967" s="12">
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
       <c r="I967" s="12">
         <v>100</v>
       </c>
       <c r="J967" s="12">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="968" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A968" s="12" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="B968" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C968" s="13">
-        <v>0.54166666666666696</v>
-      </c>
-      <c r="D968" s="12"/>
+        <v>0.5625</v>
+      </c>
+      <c r="D968" s="12">
+        <v>8</v>
+      </c>
       <c r="E968" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F968" s="12">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G968" s="12">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="H968" s="12">
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
       <c r="I968" s="12">
         <v>100</v>
       </c>
       <c r="J968" s="12">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="969" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A969" s="12" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="B969" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C969" s="13">
-        <v>0.55208333333333304</v>
-      </c>
-      <c r="D969" s="12"/>
+        <v>0.57291666666666696</v>
+      </c>
+      <c r="D969" s="12">
+        <v>4</v>
+      </c>
       <c r="E969" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F969" s="12">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G969" s="12">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="H969" s="12">
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
       <c r="I969" s="12">
         <v>100</v>
       </c>
       <c r="J969" s="12">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="970" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A970" s="12" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="B970" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C970" s="13">
-        <v>0.5625</v>
-      </c>
-      <c r="D970" s="12"/>
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D970" s="12">
+        <v>3</v>
+      </c>
       <c r="E970" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F970" s="12">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G970" s="12">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="H970" s="12">
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
       <c r="I970" s="12">
         <v>100</v>
       </c>
       <c r="J970" s="12">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="971" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A971" s="12" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="B971" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C971" s="13">
-        <v>0.57291666666666696</v>
-      </c>
-      <c r="D971" s="12"/>
+        <v>0.59375</v>
+      </c>
+      <c r="D971" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E971" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F971" s="12">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G971" s="12">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="H971" s="12">
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
       <c r="I971" s="12">
         <v>100</v>
       </c>
       <c r="J971" s="12">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="972" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A972" s="12" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="B972" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C972" s="13">
-        <v>0.58333333333333304</v>
-      </c>
-      <c r="D972" s="12"/>
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="D972" s="12">
+        <v>4</v>
+      </c>
       <c r="E972" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F972" s="12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G972" s="12">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="H972" s="12">
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
       <c r="I972" s="12">
         <v>100</v>
       </c>
       <c r="J972" s="12">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="973" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A973" s="12" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="B973" s="12" t="s">
         <v>714</v>
       </c>
       <c r="C973" s="13">
-        <v>0.59375</v>
-      </c>
-      <c r="D973" s="12"/>
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="D973" s="12">
+        <v>6</v>
+      </c>
       <c r="E973" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F973" s="12">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G973" s="12">
         <v>13.4</v>
@@ -33656,20 +33814,22 @@
     </row>
     <row r="974" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A974" s="12" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="B974" s="12" t="s">
         <v>714</v>
       </c>
       <c r="C974" s="13">
-        <v>0.61458333333333337</v>
-      </c>
-      <c r="D974" s="12"/>
+        <v>0.5</v>
+      </c>
+      <c r="D974" s="12">
+        <v>2</v>
+      </c>
       <c r="E974" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F974" s="12">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G974" s="12">
         <v>13.4</v>
@@ -33686,20 +33846,22 @@
     </row>
     <row r="975" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A975" s="12" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="B975" s="12" t="s">
         <v>714</v>
       </c>
       <c r="C975" s="13">
-        <v>0.625</v>
-      </c>
-      <c r="D975" s="12"/>
+        <v>0.5</v>
+      </c>
+      <c r="D975" s="12">
+        <v>6</v>
+      </c>
       <c r="E975" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F975" s="12">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G975" s="12">
         <v>13.4</v>
@@ -33716,735 +33878,785 @@
     </row>
     <row r="976" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A976" s="12" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="B976" s="12" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C976" s="13">
-        <v>0.48958333333333331</v>
-      </c>
-      <c r="D976" s="12"/>
+        <v>0.51041666666666696</v>
+      </c>
+      <c r="D976" s="12">
+        <v>4</v>
+      </c>
       <c r="E976" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F976" s="12">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G976" s="12">
-        <v>16.7</v>
+        <v>13.4</v>
       </c>
       <c r="H976" s="12">
-        <v>20.3</v>
+        <v>18.5</v>
       </c>
       <c r="I976" s="12">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="J976" s="12">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="977" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A977" s="12" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="B977" s="12" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C977" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="D977" s="12"/>
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="D977" s="12">
+        <v>4</v>
+      </c>
       <c r="E977" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F977" s="12">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G977" s="12">
-        <v>16.7</v>
+        <v>13.4</v>
       </c>
       <c r="H977" s="12">
-        <v>20.3</v>
+        <v>18.5</v>
       </c>
       <c r="I977" s="12">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="J977" s="12">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="978" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A978" s="12" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="B978" s="12" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C978" s="13">
-        <v>0.51041666666666696</v>
-      </c>
-      <c r="D978" s="12"/>
+        <v>0.53125</v>
+      </c>
+      <c r="D978" s="12">
+        <v>2</v>
+      </c>
       <c r="E978" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F978" s="12">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G978" s="12">
-        <v>16.7</v>
+        <v>13.4</v>
       </c>
       <c r="H978" s="12">
-        <v>20.3</v>
+        <v>18.5</v>
       </c>
       <c r="I978" s="12">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="J978" s="12">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="979" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A979" s="12" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="B979" s="12" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C979" s="13">
-        <v>0.52083333333333304</v>
-      </c>
-      <c r="D979" s="12"/>
+        <v>0.53125</v>
+      </c>
+      <c r="D979" s="12">
+        <v>4</v>
+      </c>
       <c r="E979" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F979" s="12">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G979" s="12">
-        <v>16.7</v>
+        <v>13.4</v>
       </c>
       <c r="H979" s="12">
-        <v>20.3</v>
+        <v>18.5</v>
       </c>
       <c r="I979" s="12">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="J979" s="12">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="980" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A980" s="12" t="s">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="B980" s="12" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C980" s="13">
         <v>0.53125</v>
       </c>
-      <c r="D980" s="12"/>
+      <c r="D980" s="12">
+        <v>6</v>
+      </c>
       <c r="E980" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F980" s="12">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G980" s="12">
-        <v>16.7</v>
+        <v>13.4</v>
       </c>
       <c r="H980" s="12">
-        <v>20.3</v>
+        <v>18.5</v>
       </c>
       <c r="I980" s="12">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="J980" s="12">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="981" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A981" s="12" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="B981" s="12" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C981" s="13">
         <v>0.54166666666666696</v>
       </c>
-      <c r="D981" s="12"/>
+      <c r="D981" s="12">
+        <v>6</v>
+      </c>
       <c r="E981" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F981" s="12">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G981" s="12">
-        <v>16.7</v>
+        <v>13.4</v>
       </c>
       <c r="H981" s="12">
-        <v>20.3</v>
+        <v>18.5</v>
       </c>
       <c r="I981" s="12">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="J981" s="12">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="982" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A982" s="12" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="B982" s="12" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C982" s="13">
         <v>0.55208333333333304</v>
       </c>
-      <c r="D982" s="12"/>
+      <c r="D982" s="12">
+        <v>6</v>
+      </c>
       <c r="E982" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F982" s="12">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G982" s="12">
-        <v>16.7</v>
+        <v>13.4</v>
       </c>
       <c r="H982" s="12">
-        <v>20.3</v>
+        <v>18.5</v>
       </c>
       <c r="I982" s="12">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="J982" s="12">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="983" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A983" s="12" t="s">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="B983" s="12" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C983" s="13">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D983" s="12"/>
+        <v>0.5625</v>
+      </c>
+      <c r="D983" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E983" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F983" s="12">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G983" s="12">
-        <v>16.5</v>
+        <v>13.4</v>
       </c>
       <c r="H983" s="12">
-        <v>23.9</v>
+        <v>18.5</v>
       </c>
       <c r="I983" s="12">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="J983" s="12">
-        <v>36</v>
+        <v>63</v>
       </c>
     </row>
     <row r="984" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A984" s="12" t="s">
-        <v>627</v>
+        <v>613</v>
       </c>
       <c r="B984" s="12" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C984" s="13">
-        <v>0.57291666666666663</v>
-      </c>
-      <c r="D984" s="12"/>
+        <v>0.5625</v>
+      </c>
+      <c r="D984" s="12">
+        <v>4</v>
+      </c>
       <c r="E984" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F984" s="12">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G984" s="12">
-        <v>16.5</v>
+        <v>13.4</v>
       </c>
       <c r="H984" s="12">
-        <v>23.9</v>
+        <v>18.5</v>
       </c>
       <c r="I984" s="12">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="J984" s="12">
-        <v>36</v>
+        <v>63</v>
       </c>
     </row>
     <row r="985" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A985" s="12" t="s">
-        <v>628</v>
+        <v>614</v>
       </c>
       <c r="B985" s="12" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C985" s="13">
-        <v>0.61458333333333337</v>
-      </c>
-      <c r="D985" s="12"/>
+        <v>0.57291666666666696</v>
+      </c>
+      <c r="D985" s="12">
+        <v>4</v>
+      </c>
       <c r="E985" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F985" s="12">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G985" s="12">
-        <v>16.5</v>
+        <v>13.4</v>
       </c>
       <c r="H985" s="12">
-        <v>23.9</v>
+        <v>18.5</v>
       </c>
       <c r="I985" s="12">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="J985" s="12">
-        <v>36</v>
+        <v>63</v>
       </c>
     </row>
     <row r="986" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A986" s="12" t="s">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="B986" s="12" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="C986" s="13">
-        <v>0.46875</v>
-      </c>
-      <c r="D986" s="12"/>
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D986" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E986" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F986" s="12">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G986" s="12">
-        <v>16.5</v>
+        <v>13.4</v>
       </c>
       <c r="H986" s="12">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="I986" s="12">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J986" s="12">
-        <v>100</v>
+        <v>63</v>
       </c>
     </row>
     <row r="987" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A987" s="12" t="s">
-        <v>630</v>
+        <v>616</v>
       </c>
       <c r="B987" s="12" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="C987" s="13">
-        <v>0.4375</v>
-      </c>
-      <c r="D987" s="12"/>
+        <v>0.59375</v>
+      </c>
+      <c r="D987" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E987" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F987" s="12">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G987" s="12">
-        <v>15.6</v>
+        <v>13.4</v>
       </c>
       <c r="H987" s="12">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="I987" s="12">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J987" s="12">
-        <v>83</v>
+        <v>63</v>
       </c>
     </row>
     <row r="988" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A988" s="12" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B988" s="12" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="C988" s="13">
-        <v>0.44791666666666669</v>
-      </c>
-      <c r="D988" s="12"/>
+        <v>0.59375</v>
+      </c>
+      <c r="D988" s="12">
+        <v>4</v>
+      </c>
       <c r="E988" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F988" s="12">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G988" s="12">
-        <v>15.6</v>
+        <v>13.4</v>
       </c>
       <c r="H988" s="12">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="I988" s="12">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J988" s="12">
-        <v>83</v>
+        <v>63</v>
       </c>
     </row>
     <row r="989" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A989" s="12" t="s">
-        <v>632</v>
+        <v>617</v>
       </c>
       <c r="B989" s="12" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="C989" s="13">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D989" s="12"/>
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D989" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E989" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F989" s="12">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G989" s="12">
-        <v>15.6</v>
+        <v>13.4</v>
       </c>
       <c r="H989" s="12">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="I989" s="12">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J989" s="12">
-        <v>83</v>
+        <v>63</v>
       </c>
     </row>
     <row r="990" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A990" s="12" t="s">
-        <v>633</v>
+        <v>618</v>
       </c>
       <c r="B990" s="12" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="C990" s="13">
-        <v>0.46875</v>
-      </c>
-      <c r="D990" s="12"/>
+        <v>0.625</v>
+      </c>
+      <c r="D990" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E990" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F990" s="12">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G990" s="12">
-        <v>15.6</v>
+        <v>13.4</v>
       </c>
       <c r="H990" s="12">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="I990" s="12">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J990" s="12">
-        <v>83</v>
+        <v>63</v>
       </c>
     </row>
     <row r="991" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A991" s="12" t="s">
-        <v>634</v>
+        <v>619</v>
       </c>
       <c r="B991" s="12" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="C991" s="13">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="D991" s="12"/>
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="D991" s="12">
+        <v>4</v>
+      </c>
       <c r="E991" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F991" s="12">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G991" s="12">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="H991" s="12">
-        <v>18.2</v>
+        <v>20.3</v>
       </c>
       <c r="I991" s="12">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="J991" s="12">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="992" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A992" s="12" t="s">
-        <v>635</v>
+        <v>620</v>
       </c>
       <c r="B992" s="12" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="C992" s="13">
-        <v>0.48958333333333298</v>
-      </c>
-      <c r="D992" s="12"/>
+        <v>0.5</v>
+      </c>
+      <c r="D992" s="12">
+        <v>4</v>
+      </c>
       <c r="E992" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F992" s="12">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G992" s="12">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="H992" s="12">
-        <v>18.2</v>
+        <v>20.3</v>
       </c>
       <c r="I992" s="12">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="J992" s="12">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="993" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A993" s="12" t="s">
-        <v>636</v>
+        <v>621</v>
       </c>
       <c r="B993" s="12" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="C993" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="D993" s="12"/>
+        <v>0.51041666666666696</v>
+      </c>
+      <c r="D993" s="12">
+        <v>4</v>
+      </c>
       <c r="E993" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F993" s="12">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G993" s="12">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="H993" s="12">
-        <v>18.2</v>
+        <v>20.3</v>
       </c>
       <c r="I993" s="12">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="J993" s="12">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="994" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A994" s="12" t="s">
-        <v>637</v>
+        <v>621</v>
       </c>
       <c r="B994" s="12" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="C994" s="13">
         <v>0.51041666666666696</v>
       </c>
-      <c r="D994" s="12"/>
+      <c r="D994" s="12">
+        <v>6</v>
+      </c>
       <c r="E994" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F994" s="12">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G994" s="12">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="H994" s="12">
-        <v>18.2</v>
+        <v>20.3</v>
       </c>
       <c r="I994" s="12">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="J994" s="12">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="995" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A995" s="12" t="s">
-        <v>638</v>
+        <v>622</v>
       </c>
       <c r="B995" s="12" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="C995" s="13">
-        <v>0.625</v>
-      </c>
-      <c r="D995" s="12"/>
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="D995" s="12">
+        <v>4</v>
+      </c>
       <c r="E995" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F995" s="12">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G995" s="12">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="H995" s="12">
-        <v>18.2</v>
+        <v>20.3</v>
       </c>
       <c r="I995" s="12">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="J995" s="12">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="996" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A996" s="12" t="s">
-        <v>639</v>
+        <v>622</v>
       </c>
       <c r="B996" s="12" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="C996" s="13">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="D996" s="12"/>
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="D996" s="12">
+        <v>6</v>
+      </c>
       <c r="E996" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F996" s="12">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G996" s="12">
-        <v>18</v>
+        <v>16.7</v>
       </c>
       <c r="H996" s="12">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="I996" s="12">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="J996" s="12">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="997" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A997" s="12" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="B997" s="12" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="C997" s="13">
-        <v>0.4375</v>
-      </c>
-      <c r="D997" s="12"/>
+        <v>0.53125</v>
+      </c>
+      <c r="D997" s="12">
+        <v>4</v>
+      </c>
       <c r="E997" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F997" s="12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G997" s="12">
-        <v>18</v>
+        <v>16.7</v>
       </c>
       <c r="H997" s="12">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="I997" s="12">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="J997" s="12">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="998" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A998" s="12" t="s">
-        <v>641</v>
+        <v>623</v>
       </c>
       <c r="B998" s="12" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="C998" s="13">
-        <v>0.44791666666666702</v>
-      </c>
-      <c r="D998" s="12"/>
+        <v>0.53125</v>
+      </c>
+      <c r="D998" s="12">
+        <v>2</v>
+      </c>
       <c r="E998" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F998" s="12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G998" s="12">
-        <v>18</v>
+        <v>16.7</v>
       </c>
       <c r="H998" s="12">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="I998" s="12">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="J998" s="12">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="999" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A999" s="12" t="s">
-        <v>642</v>
+        <v>623</v>
       </c>
       <c r="B999" s="12" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="C999" s="13">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D999" s="12"/>
+        <v>0.53125</v>
+      </c>
+      <c r="D999" s="12">
+        <v>6</v>
+      </c>
       <c r="E999" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F999" s="12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G999" s="12">
-        <v>18</v>
+        <v>16.7</v>
       </c>
       <c r="H999" s="12">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="I999" s="12">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="J999" s="12">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1000" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1000" s="12" t="s">
-        <v>643</v>
+        <v>624</v>
       </c>
       <c r="B1000" s="12" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="C1000" s="13">
-        <v>0.46875</v>
-      </c>
-      <c r="D1000" s="12"/>
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="D1000" s="12">
+        <v>2</v>
+      </c>
       <c r="E1000" s="12" t="s">
         <v>596</v>
       </c>
@@ -34452,29 +34664,31 @@
         <v>24</v>
       </c>
       <c r="G1000" s="12">
-        <v>18</v>
+        <v>16.7</v>
       </c>
       <c r="H1000" s="12">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="I1000" s="12">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="J1000" s="12">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1001" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1001" s="12" t="s">
-        <v>644</v>
+        <v>624</v>
       </c>
       <c r="B1001" s="12" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="C1001" s="13">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="D1001" s="12"/>
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="D1001" s="12">
+        <v>6</v>
+      </c>
       <c r="E1001" s="12" t="s">
         <v>596</v>
       </c>
@@ -34482,479 +34696,511 @@
         <v>24</v>
       </c>
       <c r="G1001" s="12">
-        <v>18</v>
+        <v>16.7</v>
       </c>
       <c r="H1001" s="12">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="I1001" s="12">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="J1001" s="12">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1002" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1002" s="12" t="s">
-        <v>645</v>
+        <v>625</v>
       </c>
       <c r="B1002" s="12" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="C1002" s="13">
-        <v>0.48958333333333298</v>
-      </c>
-      <c r="D1002" s="12"/>
+        <v>0.55208333333333304</v>
+      </c>
+      <c r="D1002" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1002" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1002" s="12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G1002" s="12">
-        <v>18</v>
+        <v>16.7</v>
       </c>
       <c r="H1002" s="12">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="I1002" s="12">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="J1002" s="12">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1003" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1003" s="12" t="s">
-        <v>646</v>
+        <v>626</v>
       </c>
       <c r="B1003" s="12" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C1003" s="13">
-        <v>0.53125</v>
-      </c>
-      <c r="D1003" s="12"/>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D1003" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1003" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1003" s="12">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G1003" s="12">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="H1003" s="12">
-        <v>20</v>
+        <v>23.9</v>
       </c>
       <c r="I1003" s="12">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="J1003" s="12">
-        <v>79</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1004" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1004" s="12" t="s">
-        <v>647</v>
+        <v>627</v>
       </c>
       <c r="B1004" s="12" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C1004" s="13">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="D1004" s="12"/>
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="D1004" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1004" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1004" s="12">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G1004" s="12">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="H1004" s="12">
-        <v>20</v>
+        <v>23.9</v>
       </c>
       <c r="I1004" s="12">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="J1004" s="12">
-        <v>79</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1005" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1005" s="12" t="s">
-        <v>648</v>
+        <v>628</v>
       </c>
       <c r="B1005" s="12" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C1005" s="13">
-        <v>0.5625</v>
-      </c>
-      <c r="D1005" s="12"/>
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D1005" s="12">
+        <v>2</v>
+      </c>
       <c r="E1005" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1005" s="12">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G1005" s="12">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="H1005" s="12">
-        <v>20</v>
+        <v>23.9</v>
       </c>
       <c r="I1005" s="12">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="J1005" s="12">
-        <v>79</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1006" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1006" s="12" t="s">
-        <v>649</v>
+        <v>629</v>
       </c>
       <c r="B1006" s="12" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C1006" s="13">
-        <v>0.57291666666666696</v>
-      </c>
-      <c r="D1006" s="12"/>
+        <v>0.46875</v>
+      </c>
+      <c r="D1006" s="12">
+        <v>4</v>
+      </c>
       <c r="E1006" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1006" s="12">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G1006" s="12">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="H1006" s="12">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I1006" s="12">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J1006" s="12">
-        <v>79</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1007" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1007" s="12" t="s">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="B1007" s="12" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C1007" s="13">
-        <v>0.58333333333333304</v>
-      </c>
-      <c r="D1007" s="12"/>
+        <v>0.4375</v>
+      </c>
+      <c r="D1007" s="12">
+        <v>6</v>
+      </c>
       <c r="E1007" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1007" s="12">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G1007" s="12">
-        <v>18</v>
+        <v>15.6</v>
       </c>
       <c r="H1007" s="12">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="I1007" s="12">
         <v>95</v>
       </c>
       <c r="J1007" s="12">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1008" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1008" s="12" t="s">
-        <v>651</v>
+        <v>631</v>
       </c>
       <c r="B1008" s="12" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C1008" s="13">
-        <v>0.59375</v>
-      </c>
-      <c r="D1008" s="12"/>
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D1008" s="12">
+        <v>6</v>
+      </c>
       <c r="E1008" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1008" s="12">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G1008" s="12">
-        <v>18</v>
+        <v>15.6</v>
       </c>
       <c r="H1008" s="12">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="I1008" s="12">
         <v>95</v>
       </c>
       <c r="J1008" s="12">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1009" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1009" s="12" t="s">
-        <v>652</v>
+        <v>632</v>
       </c>
       <c r="B1009" s="12" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C1009" s="13">
-        <v>0.60416666666666696</v>
-      </c>
-      <c r="D1009" s="12"/>
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D1009" s="12">
+        <v>6</v>
+      </c>
       <c r="E1009" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1009" s="12">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G1009" s="12">
-        <v>18</v>
+        <v>15.6</v>
       </c>
       <c r="H1009" s="12">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="I1009" s="12">
         <v>95</v>
       </c>
       <c r="J1009" s="12">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1010" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1010" s="12" t="s">
-        <v>653</v>
+        <v>633</v>
       </c>
       <c r="B1010" s="12" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C1010" s="13">
-        <v>0.61458333333333304</v>
-      </c>
-      <c r="D1010" s="12"/>
+        <v>0.46875</v>
+      </c>
+      <c r="D1010" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1010" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1010" s="12">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G1010" s="12">
-        <v>18</v>
+        <v>15.6</v>
       </c>
       <c r="H1010" s="12">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="I1010" s="12">
         <v>95</v>
       </c>
       <c r="J1010" s="12">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1011" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1011" s="12" t="s">
-        <v>654</v>
+        <v>633</v>
       </c>
       <c r="B1011" s="12" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C1011" s="13">
-        <v>0.625</v>
-      </c>
-      <c r="D1011" s="12"/>
+        <v>0.46875</v>
+      </c>
+      <c r="D1011" s="12">
+        <v>6</v>
+      </c>
       <c r="E1011" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1011" s="12">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G1011" s="12">
-        <v>18</v>
+        <v>15.6</v>
       </c>
       <c r="H1011" s="12">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="I1011" s="12">
         <v>95</v>
       </c>
       <c r="J1011" s="12">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1012" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1012" s="12" t="s">
-        <v>655</v>
+        <v>634</v>
       </c>
       <c r="B1012" s="12" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C1012" s="13">
-        <v>0.63541666666666596</v>
-      </c>
-      <c r="D1012" s="12"/>
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="D1012" s="12">
+        <v>6</v>
+      </c>
       <c r="E1012" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1012" s="12">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G1012" s="12">
-        <v>18</v>
+        <v>15.6</v>
       </c>
       <c r="H1012" s="12">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="I1012" s="12">
         <v>95</v>
       </c>
       <c r="J1012" s="12">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1013" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1013" s="12" t="s">
-        <v>656</v>
+        <v>635</v>
       </c>
       <c r="B1013" s="12" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C1013" s="13">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D1013" s="12"/>
+        <v>0.48958333333333298</v>
+      </c>
+      <c r="D1013" s="12">
+        <v>6</v>
+      </c>
       <c r="E1013" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1013" s="12">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G1013" s="12">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="H1013" s="12">
-        <v>18.100000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="I1013" s="12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J1013" s="12">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1014" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1014" s="12" t="s">
-        <v>657</v>
+        <v>636</v>
       </c>
       <c r="B1014" s="12" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C1014" s="13">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="D1014" s="12"/>
+        <v>0.5</v>
+      </c>
+      <c r="D1014" s="12">
+        <v>6</v>
+      </c>
       <c r="E1014" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1014" s="12">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G1014" s="12">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="H1014" s="12">
-        <v>18.100000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="I1014" s="12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J1014" s="12">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1015" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1015" s="12" t="s">
-        <v>658</v>
+        <v>637</v>
       </c>
       <c r="B1015" s="12" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C1015" s="13">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="D1015" s="12"/>
+        <v>0.51041666666666696</v>
+      </c>
+      <c r="D1015" s="12">
+        <v>6</v>
+      </c>
       <c r="E1015" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1015" s="12">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G1015" s="12">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="H1015" s="12">
-        <v>18.100000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="I1015" s="12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J1015" s="12">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1016" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1016" s="12" t="s">
-        <v>659</v>
+        <v>638</v>
       </c>
       <c r="B1016" s="12" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C1016" s="13">
-        <v>0.5625</v>
-      </c>
-      <c r="D1016" s="12"/>
+        <v>0.625</v>
+      </c>
+      <c r="D1016" s="12">
+        <v>2</v>
+      </c>
       <c r="E1016" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1016" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G1016" s="12">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="H1016" s="12">
-        <v>18.100000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="I1016" s="12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J1016" s="12">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1017" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1017" s="12" t="s">
-        <v>660</v>
+        <v>639</v>
       </c>
       <c r="B1017" s="12" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C1017" s="13">
-        <v>0.57291666666666663</v>
-      </c>
-      <c r="D1017" s="12"/>
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D1017" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1017" s="12" t="s">
         <v>596</v>
       </c>
@@ -34962,479 +35208,511 @@
         <v>20</v>
       </c>
       <c r="G1017" s="12">
-        <v>15.1</v>
+        <v>18</v>
       </c>
       <c r="H1017" s="12">
-        <v>18.100000000000001</v>
+        <v>20</v>
       </c>
       <c r="I1017" s="12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J1017" s="12">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1018" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1018" s="12" t="s">
-        <v>661</v>
+        <v>640</v>
       </c>
       <c r="B1018" s="12" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C1018" s="13">
-        <v>0.58333333333333304</v>
-      </c>
-      <c r="D1018" s="12"/>
+        <v>0.4375</v>
+      </c>
+      <c r="D1018" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1018" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1018" s="12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1018" s="12">
-        <v>15.1</v>
+        <v>18</v>
       </c>
       <c r="H1018" s="12">
-        <v>18.100000000000001</v>
+        <v>20</v>
       </c>
       <c r="I1018" s="12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J1018" s="12">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1019" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1019" s="12" t="s">
-        <v>662</v>
+        <v>641</v>
       </c>
       <c r="B1019" s="12" t="s">
-        <v>216</v>
+        <v>719</v>
       </c>
       <c r="C1019" s="13">
-        <v>0.38541666666666669</v>
-      </c>
-      <c r="D1019" s="12"/>
+        <v>0.44791666666666702</v>
+      </c>
+      <c r="D1019" s="12">
+        <v>6</v>
+      </c>
       <c r="E1019" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1019" s="12">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G1019" s="12">
-        <v>11.8</v>
+        <v>18</v>
       </c>
       <c r="H1019" s="12">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I1019" s="12">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J1019" s="12">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1020" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1020" s="12" t="s">
-        <v>663</v>
+        <v>642</v>
       </c>
       <c r="B1020" s="12" t="s">
-        <v>216</v>
+        <v>719</v>
       </c>
       <c r="C1020" s="13">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="D1020" s="12"/>
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D1020" s="12">
+        <v>6</v>
+      </c>
       <c r="E1020" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1020" s="12">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G1020" s="12">
-        <v>11.8</v>
+        <v>18</v>
       </c>
       <c r="H1020" s="12">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I1020" s="12">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J1020" s="12">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1021" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1021" s="12" t="s">
-        <v>664</v>
+        <v>643</v>
       </c>
       <c r="B1021" s="12" t="s">
-        <v>216</v>
+        <v>719</v>
       </c>
       <c r="C1021" s="13">
-        <v>0.40625</v>
-      </c>
-      <c r="D1021" s="12"/>
+        <v>0.46875</v>
+      </c>
+      <c r="D1021" s="12">
+        <v>6</v>
+      </c>
       <c r="E1021" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1021" s="12">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G1021" s="12">
-        <v>11.8</v>
+        <v>18</v>
       </c>
       <c r="H1021" s="12">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I1021" s="12">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J1021" s="12">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1022" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1022" s="12" t="s">
-        <v>665</v>
+        <v>644</v>
       </c>
       <c r="B1022" s="12" t="s">
-        <v>216</v>
+        <v>719</v>
       </c>
       <c r="C1022" s="13">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="D1022" s="12"/>
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="D1022" s="12">
+        <v>6</v>
+      </c>
       <c r="E1022" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1022" s="12">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G1022" s="12">
-        <v>11.8</v>
+        <v>18</v>
       </c>
       <c r="H1022" s="12">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I1022" s="12">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J1022" s="12">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1023" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1023" s="12" t="s">
-        <v>666</v>
+        <v>645</v>
       </c>
       <c r="B1023" s="12" t="s">
-        <v>216</v>
+        <v>719</v>
       </c>
       <c r="C1023" s="13">
-        <v>0.42708333333333298</v>
-      </c>
-      <c r="D1023" s="12"/>
+        <v>0.48958333333333298</v>
+      </c>
+      <c r="D1023" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1023" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1023" s="12">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G1023" s="12">
-        <v>11.8</v>
+        <v>18</v>
       </c>
       <c r="H1023" s="12">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I1023" s="12">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J1023" s="12">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1024" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1024" s="12" t="s">
-        <v>667</v>
+        <v>646</v>
       </c>
       <c r="B1024" s="12" t="s">
-        <v>216</v>
+        <v>719</v>
       </c>
       <c r="C1024" s="13">
-        <v>0.4375</v>
-      </c>
-      <c r="D1024" s="12"/>
+        <v>0.53125</v>
+      </c>
+      <c r="D1024" s="12">
+        <v>5</v>
+      </c>
       <c r="E1024" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1024" s="12">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G1024" s="12">
-        <v>11.8</v>
+        <v>18</v>
       </c>
       <c r="H1024" s="12">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I1024" s="12">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J1024" s="12">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1025" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1025" s="12" t="s">
-        <v>668</v>
+        <v>647</v>
       </c>
       <c r="B1025" s="12" t="s">
-        <v>216</v>
+        <v>719</v>
       </c>
       <c r="C1025" s="13">
-        <v>0.44791666666666602</v>
-      </c>
-      <c r="D1025" s="12"/>
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="D1025" s="12">
+        <v>4</v>
+      </c>
       <c r="E1025" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1025" s="12">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G1025" s="12">
-        <v>11.8</v>
+        <v>18</v>
       </c>
       <c r="H1025" s="12">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I1025" s="12">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J1025" s="12">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1026" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1026" s="12" t="s">
-        <v>669</v>
+        <v>648</v>
       </c>
       <c r="B1026" s="12" t="s">
-        <v>216</v>
+        <v>719</v>
       </c>
       <c r="C1026" s="13">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D1026" s="12"/>
+        <v>0.5625</v>
+      </c>
+      <c r="D1026" s="12">
+        <v>4</v>
+      </c>
       <c r="E1026" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1026" s="12">
+        <v>22</v>
+      </c>
+      <c r="G1026" s="12">
+        <v>18</v>
+      </c>
+      <c r="H1026" s="12">
         <v>20</v>
       </c>
-      <c r="G1026" s="12">
-        <v>11.8</v>
-      </c>
-      <c r="H1026" s="12">
-        <v>15</v>
-      </c>
       <c r="I1026" s="12">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J1026" s="12">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1027" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1027" s="12" t="s">
-        <v>670</v>
+        <v>649</v>
       </c>
       <c r="B1027" s="12" t="s">
-        <v>216</v>
+        <v>719</v>
       </c>
       <c r="C1027" s="13">
-        <v>0.46875</v>
-      </c>
-      <c r="D1027" s="12"/>
+        <v>0.57291666666666696</v>
+      </c>
+      <c r="D1027" s="12">
+        <v>4</v>
+      </c>
       <c r="E1027" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1027" s="12">
+        <v>22</v>
+      </c>
+      <c r="G1027" s="12">
+        <v>18</v>
+      </c>
+      <c r="H1027" s="12">
         <v>20</v>
       </c>
-      <c r="G1027" s="12">
-        <v>11.8</v>
-      </c>
-      <c r="H1027" s="12">
-        <v>15</v>
-      </c>
       <c r="I1027" s="12">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J1027" s="12">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1028" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1028" s="12" t="s">
-        <v>671</v>
+        <v>650</v>
       </c>
       <c r="B1028" s="12" t="s">
-        <v>216</v>
+        <v>719</v>
       </c>
       <c r="C1028" s="13">
-        <v>0.47916666666666602</v>
-      </c>
-      <c r="D1028" s="12"/>
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D1028" s="12">
+        <v>4</v>
+      </c>
       <c r="E1028" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1028" s="12">
+        <v>23</v>
+      </c>
+      <c r="G1028" s="12">
+        <v>18</v>
+      </c>
+      <c r="H1028" s="12">
         <v>20</v>
       </c>
-      <c r="G1028" s="12">
-        <v>11.8</v>
-      </c>
-      <c r="H1028" s="12">
-        <v>15</v>
-      </c>
       <c r="I1028" s="12">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J1028" s="12">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1029" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1029" s="12" t="s">
-        <v>672</v>
+        <v>651</v>
       </c>
       <c r="B1029" s="12" t="s">
-        <v>216</v>
+        <v>719</v>
       </c>
       <c r="C1029" s="13">
-        <v>0.48958333333333298</v>
-      </c>
-      <c r="D1029" s="12"/>
+        <v>0.59375</v>
+      </c>
+      <c r="D1029" s="12">
+        <v>4</v>
+      </c>
       <c r="E1029" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1029" s="12">
+        <v>23</v>
+      </c>
+      <c r="G1029" s="12">
+        <v>18</v>
+      </c>
+      <c r="H1029" s="12">
         <v>20</v>
       </c>
-      <c r="G1029" s="12">
-        <v>11.8</v>
-      </c>
-      <c r="H1029" s="12">
-        <v>15</v>
-      </c>
       <c r="I1029" s="12">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J1029" s="12">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1030" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1030" s="12" t="s">
-        <v>673</v>
+        <v>652</v>
       </c>
       <c r="B1030" s="12" t="s">
-        <v>216</v>
+        <v>719</v>
       </c>
       <c r="C1030" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="D1030" s="12"/>
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="D1030" s="12">
+        <v>4</v>
+      </c>
       <c r="E1030" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1030" s="12">
+        <v>22</v>
+      </c>
+      <c r="G1030" s="12">
+        <v>18</v>
+      </c>
+      <c r="H1030" s="12">
         <v>20</v>
       </c>
-      <c r="G1030" s="12">
-        <v>11.8</v>
-      </c>
-      <c r="H1030" s="12">
-        <v>15</v>
-      </c>
       <c r="I1030" s="12">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J1030" s="12">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1031" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1031" s="12" t="s">
-        <v>674</v>
+        <v>653</v>
       </c>
       <c r="B1031" s="12" t="s">
-        <v>216</v>
+        <v>719</v>
       </c>
       <c r="C1031" s="13">
-        <v>0.51041666666666696</v>
-      </c>
-      <c r="D1031" s="12"/>
+        <v>0.61458333333333304</v>
+      </c>
+      <c r="D1031" s="12">
+        <v>4</v>
+      </c>
       <c r="E1031" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1031" s="12">
+        <v>22</v>
+      </c>
+      <c r="G1031" s="12">
+        <v>18</v>
+      </c>
+      <c r="H1031" s="12">
         <v>20</v>
       </c>
-      <c r="G1031" s="12">
-        <v>11.8</v>
-      </c>
-      <c r="H1031" s="12">
-        <v>15</v>
-      </c>
       <c r="I1031" s="12">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J1031" s="12">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1032" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1032" s="12" t="s">
-        <v>675</v>
+        <v>654</v>
       </c>
       <c r="B1032" s="12" t="s">
-        <v>216</v>
+        <v>719</v>
       </c>
       <c r="C1032" s="13">
-        <v>0.52083333333333304</v>
-      </c>
-      <c r="D1032" s="12"/>
+        <v>0.625</v>
+      </c>
+      <c r="D1032" s="12">
+        <v>4</v>
+      </c>
       <c r="E1032" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1032" s="12">
+        <v>21</v>
+      </c>
+      <c r="G1032" s="12">
+        <v>18</v>
+      </c>
+      <c r="H1032" s="12">
         <v>20</v>
       </c>
-      <c r="G1032" s="12">
-        <v>11.8</v>
-      </c>
-      <c r="H1032" s="12">
-        <v>15</v>
-      </c>
       <c r="I1032" s="12">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J1032" s="12">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1033" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1033" s="12" t="s">
-        <v>676</v>
+        <v>655</v>
       </c>
       <c r="B1033" s="12" t="s">
-        <v>216</v>
+        <v>719</v>
       </c>
       <c r="C1033" s="13">
-        <v>0.53125</v>
-      </c>
-      <c r="D1033" s="12"/>
+        <v>0.63541666666666596</v>
+      </c>
+      <c r="D1033" s="12">
+        <v>4</v>
+      </c>
       <c r="E1033" s="12" t="s">
         <v>596</v>
       </c>
@@ -35442,179 +35720,191 @@
         <v>21</v>
       </c>
       <c r="G1033" s="12">
-        <v>11.8</v>
+        <v>18</v>
       </c>
       <c r="H1033" s="12">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I1033" s="12">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J1033" s="12">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1034" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1034" s="12" t="s">
-        <v>677</v>
+        <v>656</v>
       </c>
       <c r="B1034" s="12" t="s">
-        <v>216</v>
+        <v>720</v>
       </c>
       <c r="C1034" s="13">
-        <v>0.54166666666666596</v>
-      </c>
-      <c r="D1034" s="12"/>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D1034" s="12">
+        <v>5</v>
+      </c>
       <c r="E1034" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1034" s="12">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G1034" s="12">
-        <v>11.8</v>
+        <v>15.1</v>
       </c>
       <c r="H1034" s="12">
-        <v>15</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="I1034" s="12">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="J1034" s="12">
-        <v>46</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1035" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1035" s="12" t="s">
-        <v>678</v>
+        <v>656</v>
       </c>
       <c r="B1035" s="12" t="s">
-        <v>216</v>
+        <v>720</v>
       </c>
       <c r="C1035" s="13">
-        <v>0.55208333333333304</v>
-      </c>
-      <c r="D1035" s="12"/>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D1035" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1035" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1035" s="12">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G1035" s="12">
-        <v>11.8</v>
+        <v>15.1</v>
       </c>
       <c r="H1035" s="12">
-        <v>15</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="I1035" s="12">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="J1035" s="12">
-        <v>46</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1036" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1036" s="12" t="s">
-        <v>679</v>
+        <v>657</v>
       </c>
       <c r="B1036" s="12" t="s">
-        <v>216</v>
+        <v>720</v>
       </c>
       <c r="C1036" s="13">
-        <v>0.5625</v>
-      </c>
-      <c r="D1036" s="12"/>
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D1036" s="12">
+        <v>2</v>
+      </c>
       <c r="E1036" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1036" s="12">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G1036" s="12">
-        <v>11.8</v>
+        <v>15.1</v>
       </c>
       <c r="H1036" s="12">
-        <v>15</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="I1036" s="12">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="J1036" s="12">
-        <v>46</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1037" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1037" s="12" t="s">
-        <v>680</v>
+        <v>658</v>
       </c>
       <c r="B1037" s="12" t="s">
-        <v>216</v>
+        <v>720</v>
       </c>
       <c r="C1037" s="13">
-        <v>0.57291666666666596</v>
-      </c>
-      <c r="D1037" s="12"/>
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D1037" s="12">
+        <v>2</v>
+      </c>
       <c r="E1037" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1037" s="12">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G1037" s="12">
-        <v>11.8</v>
+        <v>15.1</v>
       </c>
       <c r="H1037" s="12">
-        <v>15</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="I1037" s="12">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="J1037" s="12">
-        <v>46</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1038" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1038" s="12" t="s">
-        <v>681</v>
+        <v>658</v>
       </c>
       <c r="B1038" s="12" t="s">
-        <v>216</v>
+        <v>720</v>
       </c>
       <c r="C1038" s="13">
-        <v>0.58333333333333304</v>
-      </c>
-      <c r="D1038" s="12"/>
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D1038" s="12">
+        <v>4</v>
+      </c>
       <c r="E1038" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1038" s="12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G1038" s="12">
-        <v>11.8</v>
+        <v>15.1</v>
       </c>
       <c r="H1038" s="12">
-        <v>15</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="I1038" s="12">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="J1038" s="12">
-        <v>46</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1039" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1039" s="12" t="s">
-        <v>682</v>
+        <v>658</v>
       </c>
       <c r="B1039" s="12" t="s">
-        <v>216</v>
+        <v>720</v>
       </c>
       <c r="C1039" s="13">
-        <v>0.59375</v>
-      </c>
-      <c r="D1039" s="12"/>
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D1039" s="12">
+        <v>6</v>
+      </c>
       <c r="E1039" s="12" t="s">
         <v>596</v>
       </c>
@@ -35622,299 +35912,319 @@
         <v>24</v>
       </c>
       <c r="G1039" s="12">
-        <v>11.8</v>
+        <v>15.1</v>
       </c>
       <c r="H1039" s="12">
-        <v>15</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="I1039" s="12">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="J1039" s="12">
-        <v>46</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1040" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1040" s="12" t="s">
-        <v>683</v>
+        <v>659</v>
       </c>
       <c r="B1040" s="12" t="s">
-        <v>216</v>
+        <v>720</v>
       </c>
       <c r="C1040" s="13">
-        <v>0.60416666666666596</v>
-      </c>
-      <c r="D1040" s="12"/>
+        <v>0.5625</v>
+      </c>
+      <c r="D1040" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1040" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1040" s="12">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G1040" s="12">
-        <v>11.8</v>
+        <v>15.1</v>
       </c>
       <c r="H1040" s="12">
-        <v>15</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="I1040" s="12">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="J1040" s="12">
-        <v>46</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1041" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1041" s="12" t="s">
-        <v>684</v>
+        <v>660</v>
       </c>
       <c r="B1041" s="12" t="s">
-        <v>216</v>
+        <v>720</v>
       </c>
       <c r="C1041" s="13">
-        <v>0.61458333333333304</v>
-      </c>
-      <c r="D1041" s="12"/>
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="D1041" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1041" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1041" s="12">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G1041" s="12">
-        <v>11.8</v>
+        <v>15.1</v>
       </c>
       <c r="H1041" s="12">
-        <v>15</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="I1041" s="12">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="J1041" s="12">
-        <v>46</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1042" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1042" s="12" t="s">
-        <v>685</v>
+        <v>661</v>
       </c>
       <c r="B1042" s="12" t="s">
-        <v>216</v>
+        <v>720</v>
       </c>
       <c r="C1042" s="13">
-        <v>0.624999999999999</v>
-      </c>
-      <c r="D1042" s="12"/>
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D1042" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1042" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1042" s="12">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G1042" s="12">
-        <v>11.8</v>
+        <v>15.1</v>
       </c>
       <c r="H1042" s="12">
-        <v>15</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="I1042" s="12">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="J1042" s="12">
-        <v>46</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1043" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1043" s="12" t="s">
-        <v>686</v>
+        <v>662</v>
       </c>
       <c r="B1043" s="12" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="C1043" s="13">
-        <v>0.46875</v>
-      </c>
-      <c r="D1043" s="12"/>
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="D1043" s="12">
+        <v>6</v>
+      </c>
       <c r="E1043" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1043" s="12">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G1043" s="12">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="H1043" s="12">
-        <v>16.3</v>
+        <v>15</v>
       </c>
       <c r="I1043" s="12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J1043" s="12">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1044" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1044" s="12" t="s">
-        <v>687</v>
+        <v>663</v>
       </c>
       <c r="B1044" s="12" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="C1044" s="13">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="D1044" s="12"/>
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D1044" s="12">
+        <v>6</v>
+      </c>
       <c r="E1044" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1044" s="12">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G1044" s="12">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="H1044" s="12">
-        <v>16.3</v>
+        <v>15</v>
       </c>
       <c r="I1044" s="12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J1044" s="12">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1045" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1045" s="12" t="s">
-        <v>688</v>
+        <v>664</v>
       </c>
       <c r="B1045" s="12" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="C1045" s="13">
-        <v>0.48958333333333298</v>
-      </c>
-      <c r="D1045" s="12"/>
+        <v>0.40625</v>
+      </c>
+      <c r="D1045" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1045" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1045" s="12">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G1045" s="12">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="H1045" s="12">
-        <v>16.3</v>
+        <v>15</v>
       </c>
       <c r="I1045" s="12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J1045" s="12">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1046" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1046" s="12" t="s">
-        <v>689</v>
+        <v>665</v>
       </c>
       <c r="B1046" s="12" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="C1046" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="D1046" s="12"/>
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="D1046" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1046" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1046" s="12">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G1046" s="12">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="H1046" s="12">
-        <v>16.3</v>
+        <v>15</v>
       </c>
       <c r="I1046" s="12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J1046" s="12">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1047" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1047" s="12" t="s">
-        <v>690</v>
+        <v>666</v>
       </c>
       <c r="B1047" s="12" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="C1047" s="13">
-        <v>0.51041666666666696</v>
-      </c>
-      <c r="D1047" s="12"/>
+        <v>0.42708333333333298</v>
+      </c>
+      <c r="D1047" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1047" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1047" s="12">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G1047" s="12">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="H1047" s="12">
-        <v>16.3</v>
+        <v>15</v>
       </c>
       <c r="I1047" s="12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J1047" s="12">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1048" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1048" s="12" t="s">
-        <v>691</v>
+        <v>667</v>
       </c>
       <c r="B1048" s="12" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="C1048" s="13">
-        <v>0.52083333333333304</v>
-      </c>
-      <c r="D1048" s="12"/>
+        <v>0.4375</v>
+      </c>
+      <c r="D1048" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1048" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1048" s="12">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1048" s="12">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="H1048" s="12">
-        <v>16.3</v>
+        <v>15</v>
       </c>
       <c r="I1048" s="12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J1048" s="12">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1049" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1049" s="12" t="s">
-        <v>692</v>
+        <v>668</v>
       </c>
       <c r="B1049" s="12" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="C1049" s="13">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D1049" s="12"/>
+        <v>0.44791666666666602</v>
+      </c>
+      <c r="D1049" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1049" s="12" t="s">
         <v>596</v>
       </c>
@@ -35922,29 +36232,31 @@
         <v>19</v>
       </c>
       <c r="G1049" s="12">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="H1049" s="12">
-        <v>16.3</v>
+        <v>15</v>
       </c>
       <c r="I1049" s="12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J1049" s="12">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1050" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1050" s="12" t="s">
-        <v>693</v>
+        <v>669</v>
       </c>
       <c r="B1050" s="12" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="C1050" s="13">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="D1050" s="12"/>
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D1050" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1050" s="12" t="s">
         <v>596</v>
       </c>
@@ -35952,623 +36264,1873 @@
         <v>20</v>
       </c>
       <c r="G1050" s="12">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="H1050" s="12">
-        <v>16.3</v>
+        <v>15</v>
       </c>
       <c r="I1050" s="12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J1050" s="12">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1051" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1051" s="12" t="s">
-        <v>694</v>
+        <v>670</v>
       </c>
       <c r="B1051" s="12" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="C1051" s="13">
-        <v>0.5625</v>
-      </c>
-      <c r="D1051" s="12"/>
+        <v>0.46875</v>
+      </c>
+      <c r="D1051" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1051" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1051" s="12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1051" s="12">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="H1051" s="12">
-        <v>16.3</v>
+        <v>15</v>
       </c>
       <c r="I1051" s="12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J1051" s="12">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1052" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1052" s="12" t="s">
-        <v>695</v>
+        <v>670</v>
       </c>
       <c r="B1052" s="12" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="C1052" s="13">
-        <v>0.57291666666666696</v>
-      </c>
-      <c r="D1052" s="12"/>
+        <v>0.46875</v>
+      </c>
+      <c r="D1052" s="12">
+        <v>5</v>
+      </c>
       <c r="E1052" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1052" s="12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1052" s="12">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="H1052" s="12">
-        <v>16.3</v>
+        <v>15</v>
       </c>
       <c r="I1052" s="12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J1052" s="12">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1053" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1053" s="12" t="s">
-        <v>696</v>
+        <v>671</v>
       </c>
       <c r="B1053" s="12" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="C1053" s="13">
-        <v>0.58333333333333404</v>
-      </c>
-      <c r="D1053" s="12"/>
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="D1053" s="12">
+        <v>4</v>
+      </c>
       <c r="E1053" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1053" s="12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1053" s="12">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="H1053" s="12">
-        <v>16.3</v>
+        <v>15</v>
       </c>
       <c r="I1053" s="12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J1053" s="12">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1054" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1054" s="12" t="s">
-        <v>697</v>
+        <v>672</v>
       </c>
       <c r="B1054" s="12" t="s">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="C1054" s="13">
-        <v>0.44791666666666669</v>
-      </c>
-      <c r="D1054" s="12"/>
+        <v>0.48958333333333298</v>
+      </c>
+      <c r="D1054" s="12">
+        <v>4</v>
+      </c>
       <c r="E1054" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1054" s="12">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G1054" s="12">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="H1054" s="12">
-        <v>18.399999999999999</v>
+        <v>15</v>
       </c>
       <c r="I1054" s="12">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="J1054" s="12">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1055" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1055" s="12" t="s">
-        <v>698</v>
+        <v>673</v>
       </c>
       <c r="B1055" s="12" t="s">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="C1055" s="13">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D1055" s="12"/>
+        <v>0.5</v>
+      </c>
+      <c r="D1055" s="12">
+        <v>8</v>
+      </c>
       <c r="E1055" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1055" s="12">
+        <v>20</v>
+      </c>
+      <c r="G1055" s="12">
+        <v>11.8</v>
+      </c>
+      <c r="H1055" s="12">
         <v>15</v>
       </c>
-      <c r="G1055" s="12">
-        <v>12</v>
-      </c>
-      <c r="H1055" s="12">
-        <v>18.399999999999999</v>
-      </c>
       <c r="I1055" s="12">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="J1055" s="12">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1056" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1056" s="12" t="s">
-        <v>699</v>
+        <v>674</v>
       </c>
       <c r="B1056" s="12" t="s">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="C1056" s="13">
-        <v>0.48958333333333331</v>
-      </c>
-      <c r="D1056" s="12"/>
+        <v>0.51041666666666696</v>
+      </c>
+      <c r="D1056" s="12">
+        <v>4</v>
+      </c>
       <c r="E1056" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1056" s="12">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G1056" s="12">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="H1056" s="12">
-        <v>18.399999999999999</v>
+        <v>15</v>
       </c>
       <c r="I1056" s="12">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="J1056" s="12">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1057" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1057" s="12" t="s">
-        <v>700</v>
+        <v>674</v>
       </c>
       <c r="B1057" s="12" t="s">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="C1057" s="13">
-        <v>0.5625</v>
-      </c>
-      <c r="D1057" s="12"/>
+        <v>0.51041666666666696</v>
+      </c>
+      <c r="D1057" s="12">
+        <v>5</v>
+      </c>
       <c r="E1057" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1057" s="12">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G1057" s="12">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="H1057" s="12">
-        <v>18.399999999999999</v>
+        <v>15</v>
       </c>
       <c r="I1057" s="12">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="J1057" s="12">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1058" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1058" s="12" t="s">
-        <v>701</v>
+        <v>674</v>
       </c>
       <c r="B1058" s="12" t="s">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="C1058" s="13">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="D1058" s="12"/>
+        <v>0.51041666666666696</v>
+      </c>
+      <c r="D1058" s="12">
+        <v>7</v>
+      </c>
       <c r="E1058" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1058" s="12">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G1058" s="12">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="H1058" s="12">
-        <v>18.399999999999999</v>
+        <v>15</v>
       </c>
       <c r="I1058" s="12">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="J1058" s="12">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1059" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1059" s="12" t="s">
-        <v>702</v>
+        <v>675</v>
       </c>
       <c r="B1059" s="12" t="s">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="C1059" s="13">
-        <v>0.59375</v>
-      </c>
-      <c r="D1059" s="12"/>
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="D1059" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1059" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1059" s="12">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G1059" s="12">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="H1059" s="12">
-        <v>18.399999999999999</v>
+        <v>15</v>
       </c>
       <c r="I1059" s="12">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="J1059" s="12">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1060" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1060" s="12" t="s">
-        <v>703</v>
+        <v>676</v>
       </c>
       <c r="B1060" s="12" t="s">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="C1060" s="13">
-        <v>0.60416666666666696</v>
-      </c>
-      <c r="D1060" s="12"/>
+        <v>0.53125</v>
+      </c>
+      <c r="D1060" s="12">
+        <v>4</v>
+      </c>
       <c r="E1060" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1060" s="12">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G1060" s="12">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="H1060" s="12">
-        <v>18.399999999999999</v>
+        <v>15</v>
       </c>
       <c r="I1060" s="12">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="J1060" s="12">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1061" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1061" s="12" t="s">
-        <v>704</v>
+        <v>676</v>
       </c>
       <c r="B1061" s="12" t="s">
-        <v>294</v>
+        <v>216</v>
       </c>
       <c r="C1061" s="13">
-        <v>0.4375</v>
-      </c>
-      <c r="D1061" s="12"/>
+        <v>0.53125</v>
+      </c>
+      <c r="D1061" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1061" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1061" s="12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G1061" s="12">
-        <v>13.3</v>
+        <v>11.8</v>
       </c>
       <c r="H1061" s="12">
-        <v>21.1</v>
+        <v>15</v>
       </c>
       <c r="I1061" s="12">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="J1061" s="12">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1062" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1062" s="12" t="s">
-        <v>705</v>
+        <v>677</v>
       </c>
       <c r="B1062" s="12" t="s">
-        <v>294</v>
+        <v>216</v>
       </c>
       <c r="C1062" s="13">
-        <v>0.48958333333333331</v>
-      </c>
-      <c r="D1062" s="12"/>
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="D1062" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1062" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1062" s="12">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G1062" s="12">
-        <v>13.3</v>
+        <v>11.8</v>
       </c>
       <c r="H1062" s="12">
-        <v>21.1</v>
+        <v>15</v>
       </c>
       <c r="I1062" s="12">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="J1062" s="12">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1063" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1063" s="12" t="s">
-        <v>706</v>
+        <v>677</v>
       </c>
       <c r="B1063" s="12" t="s">
-        <v>294</v>
+        <v>216</v>
       </c>
       <c r="C1063" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="D1063" s="12"/>
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="D1063" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1063" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1063" s="12">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G1063" s="12">
-        <v>13.3</v>
+        <v>11.8</v>
       </c>
       <c r="H1063" s="12">
-        <v>21.1</v>
+        <v>15</v>
       </c>
       <c r="I1063" s="12">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="J1063" s="12">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1064" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1064" s="12" t="s">
-        <v>707</v>
+        <v>678</v>
       </c>
       <c r="B1064" s="12" t="s">
-        <v>294</v>
+        <v>216</v>
       </c>
       <c r="C1064" s="13">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="D1064" s="12"/>
+        <v>0.55208333333333304</v>
+      </c>
+      <c r="D1064" s="12">
+        <v>3</v>
+      </c>
       <c r="E1064" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1064" s="12">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G1064" s="12">
-        <v>13.3</v>
+        <v>11.8</v>
       </c>
       <c r="H1064" s="12">
-        <v>21.1</v>
+        <v>15</v>
       </c>
       <c r="I1064" s="12">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="J1064" s="12">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1065" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1065" s="12" t="s">
-        <v>708</v>
+        <v>679</v>
       </c>
       <c r="B1065" s="12" t="s">
-        <v>294</v>
+        <v>216</v>
       </c>
       <c r="C1065" s="13">
-        <v>0.57291666666666663</v>
-      </c>
-      <c r="D1065" s="12"/>
+        <v>0.5625</v>
+      </c>
+      <c r="D1065" s="12">
+        <v>4</v>
+      </c>
       <c r="E1065" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1065" s="12">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G1065" s="12">
-        <v>13.3</v>
+        <v>11.8</v>
       </c>
       <c r="H1065" s="12">
-        <v>21.1</v>
+        <v>15</v>
       </c>
       <c r="I1065" s="12">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="J1065" s="12">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1066" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1066" s="12" t="s">
-        <v>709</v>
+        <v>680</v>
       </c>
       <c r="B1066" s="12" t="s">
-        <v>294</v>
+        <v>216</v>
       </c>
       <c r="C1066" s="13">
-        <v>0.59375</v>
-      </c>
-      <c r="D1066" s="12"/>
+        <v>0.57291666666666596</v>
+      </c>
+      <c r="D1066" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1066" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1066" s="12">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G1066" s="12">
-        <v>13.3</v>
+        <v>11.8</v>
       </c>
       <c r="H1066" s="12">
-        <v>21.1</v>
+        <v>15</v>
       </c>
       <c r="I1066" s="12">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="J1066" s="12">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1067" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1067" s="12" t="s">
-        <v>710</v>
+        <v>680</v>
       </c>
       <c r="B1067" s="12" t="s">
-        <v>294</v>
+        <v>216</v>
       </c>
       <c r="C1067" s="13">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D1067" s="12"/>
+        <v>0.57291666666666596</v>
+      </c>
+      <c r="D1067" s="12">
+        <v>3</v>
+      </c>
       <c r="E1067" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1067" s="12">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G1067" s="12">
-        <v>13.3</v>
+        <v>11.8</v>
       </c>
       <c r="H1067" s="12">
-        <v>21.1</v>
+        <v>15</v>
       </c>
       <c r="I1067" s="12">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="J1067" s="12">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1068" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1068" s="12" t="s">
-        <v>711</v>
+        <v>681</v>
       </c>
       <c r="B1068" s="12" t="s">
-        <v>294</v>
+        <v>216</v>
       </c>
       <c r="C1068" s="13">
-        <v>0.61458333333333337</v>
-      </c>
-      <c r="D1068" s="12"/>
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D1068" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1068" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1068" s="12">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G1068" s="12">
-        <v>13.3</v>
+        <v>11.8</v>
       </c>
       <c r="H1068" s="12">
-        <v>21.1</v>
+        <v>15</v>
       </c>
       <c r="I1068" s="12">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="J1068" s="12">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1069" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1069" s="12" t="s">
-        <v>712</v>
+        <v>682</v>
       </c>
       <c r="B1069" s="12" t="s">
-        <v>294</v>
+        <v>216</v>
       </c>
       <c r="C1069" s="13">
-        <v>0.625</v>
-      </c>
-      <c r="D1069" s="12"/>
+        <v>0.59375</v>
+      </c>
+      <c r="D1069" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="E1069" s="12" t="s">
         <v>596</v>
       </c>
       <c r="F1069" s="12">
+        <v>24</v>
+      </c>
+      <c r="G1069" s="12">
+        <v>11.8</v>
+      </c>
+      <c r="H1069" s="12">
+        <v>15</v>
+      </c>
+      <c r="I1069" s="12">
+        <v>65</v>
+      </c>
+      <c r="J1069" s="12">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1070" s="12" t="s">
+        <v>683</v>
+      </c>
+      <c r="B1070" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1070" s="13">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="D1070" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1070" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1070" s="12">
+        <v>25</v>
+      </c>
+      <c r="G1070" s="12">
+        <v>11.8</v>
+      </c>
+      <c r="H1070" s="12">
+        <v>15</v>
+      </c>
+      <c r="I1070" s="12">
+        <v>65</v>
+      </c>
+      <c r="J1070" s="12">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1071" s="12" t="s">
+        <v>683</v>
+      </c>
+      <c r="B1071" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1071" s="13">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="D1071" s="12">
+        <v>6</v>
+      </c>
+      <c r="E1071" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1071" s="12">
+        <v>25</v>
+      </c>
+      <c r="G1071" s="12">
+        <v>11.8</v>
+      </c>
+      <c r="H1071" s="12">
+        <v>15</v>
+      </c>
+      <c r="I1071" s="12">
+        <v>65</v>
+      </c>
+      <c r="J1071" s="12">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1072" s="12" t="s">
+        <v>684</v>
+      </c>
+      <c r="B1072" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1072" s="13">
+        <v>0.61458333333333304</v>
+      </c>
+      <c r="D1072" s="12">
+        <v>6</v>
+      </c>
+      <c r="E1072" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1072" s="12">
+        <v>25</v>
+      </c>
+      <c r="G1072" s="12">
+        <v>11.8</v>
+      </c>
+      <c r="H1072" s="12">
+        <v>15</v>
+      </c>
+      <c r="I1072" s="12">
+        <v>65</v>
+      </c>
+      <c r="J1072" s="12">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1073" s="12" t="s">
+        <v>685</v>
+      </c>
+      <c r="B1073" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1073" s="13">
+        <v>0.624999999999999</v>
+      </c>
+      <c r="D1073" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1073" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1073" s="12">
+        <v>25</v>
+      </c>
+      <c r="G1073" s="12">
+        <v>11.8</v>
+      </c>
+      <c r="H1073" s="12">
+        <v>15</v>
+      </c>
+      <c r="I1073" s="12">
+        <v>65</v>
+      </c>
+      <c r="J1073" s="12">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1074" s="12" t="s">
+        <v>685</v>
+      </c>
+      <c r="B1074" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1074" s="13">
+        <v>0.624999999999999</v>
+      </c>
+      <c r="D1074" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1074" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1074" s="12">
+        <v>25</v>
+      </c>
+      <c r="G1074" s="12">
+        <v>11.8</v>
+      </c>
+      <c r="H1074" s="12">
+        <v>15</v>
+      </c>
+      <c r="I1074" s="12">
+        <v>65</v>
+      </c>
+      <c r="J1074" s="12">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1075" s="12" t="s">
+        <v>685</v>
+      </c>
+      <c r="B1075" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1075" s="13">
+        <v>0.624999999999999</v>
+      </c>
+      <c r="D1075" s="12">
+        <v>4</v>
+      </c>
+      <c r="E1075" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1075" s="12">
+        <v>25</v>
+      </c>
+      <c r="G1075" s="12">
+        <v>11.8</v>
+      </c>
+      <c r="H1075" s="12">
+        <v>15</v>
+      </c>
+      <c r="I1075" s="12">
+        <v>65</v>
+      </c>
+      <c r="J1075" s="12">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1076" s="12" t="s">
+        <v>686</v>
+      </c>
+      <c r="B1076" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1076" s="13">
+        <v>0.46875</v>
+      </c>
+      <c r="D1076" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1076" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1076" s="12">
+        <v>20</v>
+      </c>
+      <c r="G1076" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="H1076" s="12">
+        <v>16.3</v>
+      </c>
+      <c r="I1076" s="12">
+        <v>70</v>
+      </c>
+      <c r="J1076" s="12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1077" s="12" t="s">
+        <v>687</v>
+      </c>
+      <c r="B1077" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1077" s="13">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D1077" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1077" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1077" s="12">
+        <v>20</v>
+      </c>
+      <c r="G1077" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="H1077" s="12">
+        <v>16.3</v>
+      </c>
+      <c r="I1077" s="12">
+        <v>70</v>
+      </c>
+      <c r="J1077" s="12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1078" s="12" t="s">
+        <v>687</v>
+      </c>
+      <c r="B1078" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1078" s="13">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D1078" s="12">
+        <v>4</v>
+      </c>
+      <c r="E1078" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1078" s="12">
+        <v>20</v>
+      </c>
+      <c r="G1078" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="H1078" s="12">
+        <v>16.3</v>
+      </c>
+      <c r="I1078" s="12">
+        <v>70</v>
+      </c>
+      <c r="J1078" s="12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1079" s="12" t="s">
+        <v>688</v>
+      </c>
+      <c r="B1079" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1079" s="13">
+        <v>0.48958333333333298</v>
+      </c>
+      <c r="D1079" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1079" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1079" s="12">
+        <v>21</v>
+      </c>
+      <c r="G1079" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="H1079" s="12">
+        <v>16.3</v>
+      </c>
+      <c r="I1079" s="12">
+        <v>70</v>
+      </c>
+      <c r="J1079" s="12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1080" s="12" t="s">
+        <v>688</v>
+      </c>
+      <c r="B1080" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1080" s="13">
+        <v>0.48958333333333298</v>
+      </c>
+      <c r="D1080" s="12">
+        <v>4</v>
+      </c>
+      <c r="E1080" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1080" s="12">
+        <v>21</v>
+      </c>
+      <c r="G1080" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="H1080" s="12">
+        <v>16.3</v>
+      </c>
+      <c r="I1080" s="12">
+        <v>70</v>
+      </c>
+      <c r="J1080" s="12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1081" s="12" t="s">
+        <v>689</v>
+      </c>
+      <c r="B1081" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1081" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="D1081" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1081" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1081" s="12">
+        <v>20</v>
+      </c>
+      <c r="G1081" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="H1081" s="12">
+        <v>16.3</v>
+      </c>
+      <c r="I1081" s="12">
+        <v>70</v>
+      </c>
+      <c r="J1081" s="12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1082" s="12" t="s">
+        <v>690</v>
+      </c>
+      <c r="B1082" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1082" s="13">
+        <v>0.51041666666666696</v>
+      </c>
+      <c r="D1082" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1082" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1082" s="12">
+        <v>20</v>
+      </c>
+      <c r="G1082" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="H1082" s="12">
+        <v>16.3</v>
+      </c>
+      <c r="I1082" s="12">
+        <v>70</v>
+      </c>
+      <c r="J1082" s="12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1083" s="12" t="s">
+        <v>691</v>
+      </c>
+      <c r="B1083" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1083" s="13">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="D1083" s="12">
+        <v>7</v>
+      </c>
+      <c r="E1083" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1083" s="12">
+        <v>20</v>
+      </c>
+      <c r="G1083" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="H1083" s="12">
+        <v>16.3</v>
+      </c>
+      <c r="I1083" s="12">
+        <v>70</v>
+      </c>
+      <c r="J1083" s="12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1084" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B1084" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1084" s="13">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D1084" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1084" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1084" s="12">
+        <v>19</v>
+      </c>
+      <c r="G1084" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="H1084" s="12">
+        <v>16.3</v>
+      </c>
+      <c r="I1084" s="12">
+        <v>70</v>
+      </c>
+      <c r="J1084" s="12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1085" s="12" t="s">
+        <v>693</v>
+      </c>
+      <c r="B1085" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1085" s="13">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="D1085" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1085" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1085" s="12">
+        <v>20</v>
+      </c>
+      <c r="G1085" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="H1085" s="12">
+        <v>16.3</v>
+      </c>
+      <c r="I1085" s="12">
+        <v>70</v>
+      </c>
+      <c r="J1085" s="12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1086" s="12" t="s">
+        <v>693</v>
+      </c>
+      <c r="B1086" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1086" s="13">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="D1086" s="12">
+        <v>6</v>
+      </c>
+      <c r="E1086" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1086" s="12">
+        <v>20</v>
+      </c>
+      <c r="G1086" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="H1086" s="12">
+        <v>16.3</v>
+      </c>
+      <c r="I1086" s="12">
+        <v>70</v>
+      </c>
+      <c r="J1086" s="12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1087" s="12" t="s">
+        <v>694</v>
+      </c>
+      <c r="B1087" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1087" s="13">
+        <v>0.5625</v>
+      </c>
+      <c r="D1087" s="12">
+        <v>6</v>
+      </c>
+      <c r="E1087" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1087" s="12">
+        <v>21</v>
+      </c>
+      <c r="G1087" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="H1087" s="12">
+        <v>16.3</v>
+      </c>
+      <c r="I1087" s="12">
+        <v>70</v>
+      </c>
+      <c r="J1087" s="12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1088" s="12" t="s">
+        <v>695</v>
+      </c>
+      <c r="B1088" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1088" s="13">
+        <v>0.57291666666666696</v>
+      </c>
+      <c r="D1088" s="12">
+        <v>6</v>
+      </c>
+      <c r="E1088" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1088" s="12">
+        <v>21</v>
+      </c>
+      <c r="G1088" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="H1088" s="12">
+        <v>16.3</v>
+      </c>
+      <c r="I1088" s="12">
+        <v>70</v>
+      </c>
+      <c r="J1088" s="12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1089" s="12" t="s">
+        <v>696</v>
+      </c>
+      <c r="B1089" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1089" s="13">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="D1089" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1089" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1089" s="12">
+        <v>21</v>
+      </c>
+      <c r="G1089" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="H1089" s="12">
+        <v>16.3</v>
+      </c>
+      <c r="I1089" s="12">
+        <v>70</v>
+      </c>
+      <c r="J1089" s="12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1090" s="12" t="s">
+        <v>697</v>
+      </c>
+      <c r="B1090" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1090" s="13">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D1090" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1090" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1090" s="12">
+        <v>14</v>
+      </c>
+      <c r="G1090" s="12">
+        <v>12</v>
+      </c>
+      <c r="H1090" s="12">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="I1090" s="12">
+        <v>80</v>
+      </c>
+      <c r="J1090" s="12">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1091" s="12" t="s">
+        <v>698</v>
+      </c>
+      <c r="B1091" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1091" s="13">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D1091" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1091" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1091" s="12">
+        <v>15</v>
+      </c>
+      <c r="G1091" s="12">
+        <v>12</v>
+      </c>
+      <c r="H1091" s="12">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="I1091" s="12">
+        <v>80</v>
+      </c>
+      <c r="J1091" s="12">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1092" s="12" t="s">
+        <v>699</v>
+      </c>
+      <c r="B1092" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1092" s="13">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="D1092" s="12">
+        <v>6</v>
+      </c>
+      <c r="E1092" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1092" s="12">
+        <v>16</v>
+      </c>
+      <c r="G1092" s="12">
+        <v>12</v>
+      </c>
+      <c r="H1092" s="12">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="I1092" s="12">
+        <v>80</v>
+      </c>
+      <c r="J1092" s="12">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1093" s="12" t="s">
+        <v>700</v>
+      </c>
+      <c r="B1093" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1093" s="13">
+        <v>0.5625</v>
+      </c>
+      <c r="D1093" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1093" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1093" s="12">
+        <v>24</v>
+      </c>
+      <c r="G1093" s="12">
+        <v>12</v>
+      </c>
+      <c r="H1093" s="12">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="I1093" s="12">
+        <v>80</v>
+      </c>
+      <c r="J1093" s="12">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1094" s="12" t="s">
+        <v>701</v>
+      </c>
+      <c r="B1094" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1094" s="13">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D1094" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1094" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1094" s="12">
+        <v>25</v>
+      </c>
+      <c r="G1094" s="12">
+        <v>12</v>
+      </c>
+      <c r="H1094" s="12">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="I1094" s="12">
+        <v>80</v>
+      </c>
+      <c r="J1094" s="12">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1095" s="12" t="s">
+        <v>702</v>
+      </c>
+      <c r="B1095" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1095" s="13">
+        <v>0.59375</v>
+      </c>
+      <c r="D1095" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1095" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1095" s="12">
+        <v>26</v>
+      </c>
+      <c r="G1095" s="12">
+        <v>12</v>
+      </c>
+      <c r="H1095" s="12">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="I1095" s="12">
+        <v>80</v>
+      </c>
+      <c r="J1095" s="12">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1096" s="12" t="s">
+        <v>703</v>
+      </c>
+      <c r="B1096" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1096" s="13">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="D1096" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1096" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1096" s="12">
+        <v>27</v>
+      </c>
+      <c r="G1096" s="12">
+        <v>12</v>
+      </c>
+      <c r="H1096" s="12">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="I1096" s="12">
+        <v>80</v>
+      </c>
+      <c r="J1096" s="12">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1097" s="12" t="s">
+        <v>703</v>
+      </c>
+      <c r="B1097" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1097" s="13">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="D1097" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1097" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1097" s="12">
+        <v>27</v>
+      </c>
+      <c r="G1097" s="12">
+        <v>12</v>
+      </c>
+      <c r="H1097" s="12">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="I1097" s="12">
+        <v>80</v>
+      </c>
+      <c r="J1097" s="12">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1098" s="12" t="s">
+        <v>703</v>
+      </c>
+      <c r="B1098" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1098" s="13">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="D1098" s="12">
+        <v>8</v>
+      </c>
+      <c r="E1098" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1098" s="12">
+        <v>27</v>
+      </c>
+      <c r="G1098" s="12">
+        <v>12</v>
+      </c>
+      <c r="H1098" s="12">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="I1098" s="12">
+        <v>80</v>
+      </c>
+      <c r="J1098" s="12">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1099" s="12" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1099" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1099" s="13">
+        <v>0.4375</v>
+      </c>
+      <c r="D1099" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1099" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1099" s="12">
+        <v>22</v>
+      </c>
+      <c r="G1099" s="12">
+        <v>13.3</v>
+      </c>
+      <c r="H1099" s="12">
+        <v>21.1</v>
+      </c>
+      <c r="I1099" s="12">
+        <v>81</v>
+      </c>
+      <c r="J1099" s="12">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1100" s="12" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1100" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1100" s="13">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="D1100" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1100" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1100" s="12">
+        <v>25</v>
+      </c>
+      <c r="G1100" s="12">
+        <v>13.3</v>
+      </c>
+      <c r="H1100" s="12">
+        <v>21.1</v>
+      </c>
+      <c r="I1100" s="12">
+        <v>81</v>
+      </c>
+      <c r="J1100" s="12">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1101" s="12" t="s">
+        <v>706</v>
+      </c>
+      <c r="B1101" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1101" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="D1101" s="12">
+        <v>7</v>
+      </c>
+      <c r="E1101" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1101" s="12">
+        <v>25</v>
+      </c>
+      <c r="G1101" s="12">
+        <v>13.3</v>
+      </c>
+      <c r="H1101" s="12">
+        <v>21.1</v>
+      </c>
+      <c r="I1101" s="12">
+        <v>81</v>
+      </c>
+      <c r="J1101" s="12">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1102" s="12" t="s">
+        <v>707</v>
+      </c>
+      <c r="B1102" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1102" s="13">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D1102" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1102" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1102" s="12">
+        <v>25</v>
+      </c>
+      <c r="G1102" s="12">
+        <v>13.3</v>
+      </c>
+      <c r="H1102" s="12">
+        <v>21.1</v>
+      </c>
+      <c r="I1102" s="12">
+        <v>81</v>
+      </c>
+      <c r="J1102" s="12">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1103" s="12" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1103" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1103" s="13">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="D1103" s="12">
+        <v>8</v>
+      </c>
+      <c r="E1103" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1103" s="12">
+        <v>28</v>
+      </c>
+      <c r="G1103" s="12">
+        <v>13.3</v>
+      </c>
+      <c r="H1103" s="12">
+        <v>21.1</v>
+      </c>
+      <c r="I1103" s="12">
+        <v>81</v>
+      </c>
+      <c r="J1103" s="12">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1104" s="12" t="s">
+        <v>709</v>
+      </c>
+      <c r="B1104" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1104" s="13">
+        <v>0.59375</v>
+      </c>
+      <c r="D1104" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1104" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1104" s="12">
+        <v>30</v>
+      </c>
+      <c r="G1104" s="12">
+        <v>13.3</v>
+      </c>
+      <c r="H1104" s="12">
+        <v>21.1</v>
+      </c>
+      <c r="I1104" s="12">
+        <v>81</v>
+      </c>
+      <c r="J1104" s="12">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1105" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1105" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1105" s="13">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D1105" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1105" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1105" s="12">
         <v>31</v>
       </c>
-      <c r="G1069" s="12">
+      <c r="G1105" s="12">
         <v>13.3</v>
       </c>
-      <c r="H1069" s="12">
+      <c r="H1105" s="12">
         <v>21.1</v>
       </c>
-      <c r="I1069" s="12">
+      <c r="I1105" s="12">
         <v>81</v>
       </c>
-      <c r="J1069" s="12">
+      <c r="J1105" s="12">
         <v>47</v>
       </c>
     </row>
-    <row r="1070" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1070" s="12"/>
-      <c r="B1070" s="12"/>
-      <c r="C1070" s="12"/>
-      <c r="D1070" s="12"/>
-      <c r="E1070" s="12"/>
-      <c r="F1070" s="12"/>
-      <c r="G1070" s="12"/>
-      <c r="H1070" s="12"/>
-      <c r="I1070" s="12"/>
-      <c r="J1070" s="12"/>
-    </row>
-    <row r="1071" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1071" s="12"/>
-      <c r="B1071" s="12"/>
-      <c r="C1071" s="12"/>
-      <c r="D1071" s="12"/>
-      <c r="E1071" s="12"/>
-      <c r="F1071" s="12"/>
-      <c r="G1071" s="12"/>
-      <c r="H1071" s="12"/>
-      <c r="I1071" s="12"/>
-      <c r="J1071" s="12"/>
-    </row>
-    <row r="1072" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1072" s="12"/>
-      <c r="B1072" s="12"/>
-      <c r="C1072" s="12"/>
-      <c r="D1072" s="12"/>
-      <c r="E1072" s="12"/>
-      <c r="F1072" s="12"/>
-      <c r="G1072" s="12"/>
-      <c r="H1072" s="12"/>
-      <c r="I1072" s="12"/>
-      <c r="J1072" s="12"/>
+    <row r="1106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1106" s="12" t="s">
+        <v>711</v>
+      </c>
+      <c r="B1106" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1106" s="13">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D1106" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1106" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1106" s="12">
+        <v>32</v>
+      </c>
+      <c r="G1106" s="12">
+        <v>13.3</v>
+      </c>
+      <c r="H1106" s="12">
+        <v>21.1</v>
+      </c>
+      <c r="I1106" s="12">
+        <v>81</v>
+      </c>
+      <c r="J1106" s="12">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1107" s="12" t="s">
+        <v>711</v>
+      </c>
+      <c r="B1107" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1107" s="13">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D1107" s="12">
+        <v>4</v>
+      </c>
+      <c r="E1107" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1107" s="12">
+        <v>32</v>
+      </c>
+      <c r="G1107" s="12">
+        <v>13.3</v>
+      </c>
+      <c r="H1107" s="12">
+        <v>21.1</v>
+      </c>
+      <c r="I1107" s="12">
+        <v>81</v>
+      </c>
+      <c r="J1107" s="12">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1108" s="12" t="s">
+        <v>712</v>
+      </c>
+      <c r="B1108" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1108" s="13">
+        <v>0.625</v>
+      </c>
+      <c r="D1108" s="12">
+        <v>4</v>
+      </c>
+      <c r="E1108" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F1108" s="12">
+        <v>31</v>
+      </c>
+      <c r="G1108" s="12">
+        <v>13.3</v>
+      </c>
+      <c r="H1108" s="12">
+        <v>21.1</v>
+      </c>
+      <c r="I1108" s="12">
+        <v>81</v>
+      </c>
+      <c r="J1108" s="12">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
